--- a/business-plan/model/Angel_Arms_Financial_Model.xlsx
+++ b/business-plan/model/Angel_Arms_Financial_Model.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="203">
   <si>
     <t xml:space="preserve">Angel Arms Horse Sanctuary — Financial Model</t>
   </si>
@@ -120,6 +120,9 @@
     <t xml:space="preserve">32-rai infrastructure (your exposure)</t>
   </si>
   <si>
+    <t xml:space="preserve">32-rai profit transferred to Sanctuary (5-yr total)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Year 1 combined net</t>
   </si>
   <si>
@@ -348,7 +351,7 @@
     <t xml:space="preserve">Subdivision survey / title-splitting</t>
   </si>
   <si>
-    <t xml:space="preserve">Marketing &amp; sales commission (% of sale revenue)</t>
+    <t xml:space="preserve">Agent fee on plot sale (% of sale revenue)</t>
   </si>
   <si>
     <t xml:space="preserve">Transfer fee (% of sale revenue, seller share)</t>
@@ -522,7 +525,7 @@
     <t xml:space="preserve">Subtotal infrastructure</t>
   </si>
   <si>
-    <t xml:space="preserve">Marketing &amp; sales commission</t>
+    <t xml:space="preserve">Agent fee (on sale)</t>
   </si>
   <si>
     <t xml:space="preserve">Deducted from proceeds</t>
@@ -531,7 +534,10 @@
     <t xml:space="preserve">Transfer fee + Specific Business Tax (est.)</t>
   </si>
   <si>
-    <t xml:space="preserve">NET MARGIN</t>
+    <t xml:space="preserve">NET MARGIN (after agent fee)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  → transferred to the Sanctuary as revenue (see Sanctuary P&amp;L)</t>
   </si>
   <si>
     <t xml:space="preserve">This piece is designed to roughly break even — it's a community-building tool, not a profit engine. Your real exposure is the infrastructure subtotal above, ideally funded from buyer deposits.</t>
@@ -553,6 +559,12 @@
   </si>
   <si>
     <t xml:space="preserve">Riding lessons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32-rai development profit share (net of agent fee)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net margin from '32-rai Economics', prorated by plots sold that year — floored at ฿0 if the development runs a loss</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL REVENUE</t>
@@ -638,7 +650,7 @@
     <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -788,6 +800,23 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="9.5"/>
+      <color rgb="FF2F6B45"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <i val="true"/>
+      <sz val="9.5"/>
+      <color rgb="FFC24A78"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -861,7 +890,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1011,6 +1040,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1174,7 +1211,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Summary!$C$18:$H$18</c:f>
+              <c:f>Summary!$C$19:$H$19</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -1200,7 +1237,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Summary!$C$19:$H$19</c:f>
+              <c:f>Summary!$C$20:$H$20</c:f>
               <c:numCache>
                 <c:formatCode>\฿#,##0;"(฿"#,##0\);\-</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1228,8 +1265,8 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="96709481"/>
-        <c:axId val="84279523"/>
+        <c:axId val="43464265"/>
+        <c:axId val="51536404"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -1284,7 +1321,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Summary!$C$18:$H$18</c:f>
+              <c:f>Summary!$C$19:$H$19</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -1310,7 +1347,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Summary!$C$20:$H$20</c:f>
+              <c:f>Summary!$C$21:$H$21</c:f>
               <c:numCache>
                 <c:formatCode>\฿#,##0;"(฿"#,##0\);\-</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1345,11 +1382,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="96709481"/>
-        <c:axId val="84279523"/>
+        <c:axId val="43464265"/>
+        <c:axId val="51536404"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="96709481"/>
+        <c:axId val="43464265"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1381,7 +1418,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84279523"/>
+        <c:crossAx val="51536404"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1389,7 +1426,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="84279523"/>
+        <c:axId val="51536404"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1465,7 +1502,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96709481"/>
+        <c:crossAx val="43464265"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1676,11 +1713,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="2513704"/>
-        <c:axId val="92888228"/>
+        <c:axId val="82041251"/>
+        <c:axId val="35534150"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="2513704"/>
+        <c:axId val="82041251"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1712,7 +1749,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92888228"/>
+        <c:crossAx val="35534150"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1720,7 +1757,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="92888228"/>
+        <c:axId val="35534150"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1762,7 +1799,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2513704"/>
+        <c:crossAx val="82041251"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1907,7 +1944,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Sanctuary P&amp;L'!$C$22:$G$22</c:f>
+              <c:f>'Sanctuary P&amp;L'!$C$23:$G$23</c:f>
               <c:numCache>
                 <c:formatCode>\฿#,##0;"(฿"#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1939,11 +1976,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="69410786"/>
-        <c:axId val="90349110"/>
+        <c:axId val="2054398"/>
+        <c:axId val="17340756"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="69410786"/>
+        <c:axId val="2054398"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1975,7 +2012,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90349110"/>
+        <c:crossAx val="17340756"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1983,7 +2020,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="90349110"/>
+        <c:axId val="17340756"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2025,7 +2062,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69410786"/>
+        <c:crossAx val="2054398"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2191,8 +2228,8 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="48527160"/>
-        <c:axId val="24334700"/>
+        <c:axId val="68199892"/>
+        <c:axId val="25305814"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2308,11 +2345,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="48527160"/>
-        <c:axId val="24334700"/>
+        <c:axId val="68199892"/>
+        <c:axId val="25305814"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="48527160"/>
+        <c:axId val="68199892"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2344,7 +2381,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24334700"/>
+        <c:crossAx val="25305814"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2352,7 +2389,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="24334700"/>
+        <c:axId val="25305814"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2428,7 +2465,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48527160"/>
+        <c:crossAx val="68199892"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2462,14 +2499,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>101160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>638640</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>81360</xdr:rowOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>81000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2477,7 +2514,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="222120" y="3962520"/>
+        <a:off x="222120" y="4152960"/>
         <a:ext cx="8639640" cy="3599640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2532,14 +2569,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>262800</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>263160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>781200</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>144000</xdr:rowOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>144360</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2547,7 +2584,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="222120" y="4705200"/>
+        <a:off x="222120" y="4896000"/>
         <a:ext cx="5759640" cy="2519640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2901,7 +2938,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:H45"/>
+  <dimension ref="B1:H46"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.5"/>
@@ -2989,8 +3026,8 @@
         <v>30</v>
       </c>
       <c r="C13" s="8" t="n">
-        <f aca="false">'Cash Flow'!D8</f>
-        <v>341800</v>
+        <f aca="false">SUM('Sanctuary P&amp;L'!C12:G12)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2998,8 +3035,8 @@
         <v>31</v>
       </c>
       <c r="C14" s="8" t="n">
-        <f aca="false">'Cash Flow'!H8</f>
-        <v>5601360</v>
+        <f aca="false">'Cash Flow'!D8</f>
+        <v>341800</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3007,111 +3044,115 @@
         <v>32</v>
       </c>
       <c r="C15" s="8" t="n">
+        <f aca="false">'Cash Flow'!H8</f>
+        <v>5601360</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="8" t="n">
         <f aca="false">'Cash Flow'!H9</f>
         <v>-37958200</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="9" t="s">
+    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="10" t="str">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="10" t="str">
         <f aca="false">'Cash Flow'!C5</f>
         <v>Year 0 (capital)</v>
       </c>
-      <c r="D18" s="10" t="str">
+      <c r="D19" s="10" t="str">
         <f aca="false">'Cash Flow'!D5</f>
         <v>Year 1</v>
       </c>
-      <c r="E18" s="10" t="str">
+      <c r="E19" s="10" t="str">
         <f aca="false">'Cash Flow'!E5</f>
         <v>Year 2</v>
       </c>
-      <c r="F18" s="10" t="str">
+      <c r="F19" s="10" t="str">
         <f aca="false">'Cash Flow'!F5</f>
         <v>Year 3</v>
       </c>
-      <c r="G18" s="10" t="str">
+      <c r="G19" s="10" t="str">
         <f aca="false">'Cash Flow'!G5</f>
         <v>Year 4</v>
       </c>
-      <c r="H18" s="10" t="str">
+      <c r="H19" s="10" t="str">
         <f aca="false">'Cash Flow'!H5</f>
         <v>Year 5</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="8" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="8" t="n">
         <f aca="false">'Cash Flow'!C8</f>
         <v>-54700000</v>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D20" s="8" t="n">
         <f aca="false">'Cash Flow'!D8</f>
         <v>341800</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E20" s="8" t="n">
         <f aca="false">'Cash Flow'!E8</f>
         <v>2175240</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F20" s="8" t="n">
         <f aca="false">'Cash Flow'!F8</f>
         <v>3721000</v>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="G20" s="8" t="n">
         <f aca="false">'Cash Flow'!G8</f>
         <v>4902400</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H20" s="8" t="n">
         <f aca="false">'Cash Flow'!H8</f>
         <v>5601360</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="8" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="8" t="n">
         <f aca="false">'Cash Flow'!C9</f>
         <v>-54700000</v>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D21" s="8" t="n">
         <f aca="false">'Cash Flow'!D9</f>
         <v>-54358200</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E21" s="8" t="n">
         <f aca="false">'Cash Flow'!E9</f>
         <v>-52182960</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F21" s="8" t="n">
         <f aca="false">'Cash Flow'!F9</f>
         <v>-48461960</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G21" s="8" t="n">
         <f aca="false">'Cash Flow'!G9</f>
         <v>-43559560</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H21" s="8" t="n">
         <f aca="false">'Cash Flow'!H9</f>
         <v>-37958200</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3119,10 +3160,15 @@
         <v>38</v>
       </c>
     </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B18:H18"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3151,17 +3197,17 @@
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -3172,7 +3218,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>23000000</v>
@@ -3180,7 +3226,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>6000000</v>
@@ -3188,7 +3234,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" s="13" t="n">
         <f aca="false">C6-C7</f>
@@ -3197,7 +3243,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" s="14" t="n">
         <v>46296</v>
@@ -3205,7 +3251,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C10" s="14" t="n">
         <v>46478</v>
@@ -3213,7 +3259,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>73600000</v>
@@ -3221,7 +3267,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" s="15" t="n">
         <v>6</v>
@@ -3229,7 +3275,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" s="13" t="n">
         <f aca="false">C11/C12</f>
@@ -3238,7 +3284,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>46569</v>
@@ -3246,7 +3292,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C15" s="16" t="n">
         <v>3</v>
@@ -3254,7 +3300,7 @@
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -3265,30 +3311,30 @@
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C19" s="15" t="n">
         <v>15</v>
@@ -3308,7 +3354,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C20" s="15" t="n">
         <v>2000</v>
@@ -3328,7 +3374,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C21" s="16" t="n">
         <v>120</v>
@@ -3348,7 +3394,7 @@
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -3359,7 +3405,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C24" s="12" t="n">
         <v>15000</v>
@@ -3367,7 +3413,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C25" s="18" t="n">
         <v>300</v>
@@ -3375,7 +3421,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C26" s="19" t="n">
         <v>0.2</v>
@@ -3383,7 +3429,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" s="18" t="n">
         <v>700</v>
@@ -3391,18 +3437,18 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" s="18" t="n">
         <v>4500</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -3413,30 +3459,30 @@
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" s="18" t="n">
         <v>1200000</v>
@@ -3456,7 +3502,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C33" s="18" t="n">
         <v>800000</v>
@@ -3476,7 +3522,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C34" s="18" t="n">
         <v>3200000</v>
@@ -3496,7 +3542,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C35" s="18" t="n">
         <v>600000</v>
@@ -3516,7 +3562,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C36" s="18" t="n">
         <v>350000</v>
@@ -3536,7 +3582,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C37" s="18" t="n">
         <v>300000</v>
@@ -3556,7 +3602,7 @@
     </row>
     <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C39" s="20"/>
       <c r="D39" s="20"/>
@@ -3567,7 +3613,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C40" s="16" t="n">
         <v>3</v>
@@ -3575,7 +3621,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C41" s="18" t="n">
         <v>2500</v>
@@ -3583,30 +3629,30 @@
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C43" s="19" t="n">
         <v>0.15</v>
@@ -3626,7 +3672,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C44" s="16" t="n">
         <v>4</v>
@@ -3634,7 +3680,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C45" s="18" t="n">
         <v>800</v>
@@ -3642,30 +3688,30 @@
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C47" s="19" t="n">
         <v>0.1</v>
@@ -3685,7 +3731,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C48" s="16" t="n">
         <v>1</v>
@@ -3693,7 +3739,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C49" s="18" t="n">
         <v>4500</v>
@@ -3701,30 +3747,30 @@
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C51" s="19" t="n">
         <v>0.15</v>
@@ -3744,7 +3790,7 @@
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C53" s="20"/>
       <c r="D53" s="20"/>
@@ -3755,30 +3801,30 @@
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F54" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C55" s="15" t="n">
         <v>6</v>
@@ -3798,7 +3844,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C56" s="18" t="n">
         <v>60</v>
@@ -3806,7 +3852,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C57" s="18" t="n">
         <v>8000</v>
@@ -3814,7 +3860,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C58" s="12" t="n">
         <v>30000</v>
@@ -3822,7 +3868,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C59" s="18" t="n">
         <v>900000</v>
@@ -3842,7 +3888,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C60" s="18" t="n">
         <v>200000</v>
@@ -3862,7 +3908,7 @@
     </row>
     <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C62" s="20"/>
       <c r="D62" s="20"/>
@@ -3873,7 +3919,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C63" s="16" t="n">
         <v>32</v>
@@ -3881,7 +3927,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C64" s="15" t="n">
         <v>5</v>
@@ -3889,7 +3935,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C65" s="21" t="n">
         <f aca="false">C63-C64</f>
@@ -3898,7 +3944,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C66" s="12" t="n">
         <v>3500000</v>
@@ -3906,7 +3952,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C67" s="18" t="n">
         <v>3500000</v>
@@ -3914,7 +3960,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C68" s="18" t="n">
         <v>2000000</v>
@@ -3922,7 +3968,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C69" s="18" t="n">
         <v>3500000</v>
@@ -3930,7 +3976,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C70" s="18" t="n">
         <v>2000000</v>
@@ -3938,7 +3984,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C71" s="18" t="n">
         <v>500000</v>
@@ -3946,7 +3992,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C72" s="18" t="n">
         <v>1500000</v>
@@ -3954,7 +4000,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C73" s="18" t="n">
         <v>800000</v>
@@ -3962,15 +4008,15 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C74" s="19" t="n">
-        <v>0.03</v>
+        <v>107</v>
+      </c>
+      <c r="C74" s="22" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C75" s="19" t="n">
         <v>0.01</v>
@@ -3978,7 +4024,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C76" s="22" t="n">
         <v>0.033</v>
@@ -3986,7 +4032,7 @@
     </row>
     <row r="78" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
@@ -3997,7 +4043,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C79" s="18" t="n">
         <v>13000000</v>
@@ -4005,7 +4051,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C80" s="18" t="n">
         <v>4500000</v>
@@ -4013,7 +4059,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C81" s="18" t="n">
         <v>2900000</v>
@@ -4021,7 +4067,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C82" s="18" t="n">
         <v>2500000</v>
@@ -4029,7 +4075,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C83" s="18" t="n">
         <v>1800000</v>
@@ -4037,7 +4083,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C84" s="18" t="n">
         <v>1500000</v>
@@ -4045,7 +4091,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C85" s="18" t="n">
         <v>1500000</v>
@@ -4053,7 +4099,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C86" s="18" t="n">
         <v>1200000</v>
@@ -4061,7 +4107,7 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C87" s="18" t="n">
         <v>900000</v>
@@ -4069,7 +4115,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C88" s="18" t="n">
         <v>800000</v>
@@ -4077,7 +4123,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C89" s="18" t="n">
         <v>600000</v>
@@ -4085,7 +4131,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C90" s="18" t="n">
         <v>500000</v>
@@ -4129,26 +4175,26 @@
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="23" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4157,14 +4203,14 @@
         <v>46296</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D6" s="8" t="n">
         <f aca="false">Assumptions!$C$7</f>
         <v>6000000</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4173,14 +4219,14 @@
         <v>46478</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D7" s="8" t="n">
         <f aca="false">Assumptions!$C$8</f>
         <v>17000000</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4189,14 +4235,14 @@
         <v>46569</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D8" s="8" t="n">
         <f aca="false">Assumptions!$C$13</f>
         <v>12266666.6666667</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4205,14 +4251,14 @@
         <v>46661</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D9" s="8" t="n">
         <f aca="false">Assumptions!$C$13</f>
         <v>12266666.6666667</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4221,14 +4267,14 @@
         <v>46753</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D10" s="8" t="n">
         <f aca="false">Assumptions!$C$13</f>
         <v>12266666.6666667</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4237,14 +4283,14 @@
         <v>46844</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D11" s="8" t="n">
         <f aca="false">Assumptions!$C$13</f>
         <v>12266666.6666667</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4253,14 +4299,14 @@
         <v>46935</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D12" s="8" t="n">
         <f aca="false">Assumptions!$C$13</f>
         <v>12266666.6666667</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4269,19 +4315,19 @@
         <v>47027</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D13" s="8" t="n">
         <f aca="false">Assumptions!$C$13</f>
         <v>12266666.6666667</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D15" s="28" t="n">
         <f aca="false">SUM(D6:D13)</f>
@@ -4290,7 +4336,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D16" s="13" t="n">
         <f aca="false">SUMIF(E6:E13,"You",D6:D13)</f>
@@ -4299,7 +4345,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D17" s="13" t="n">
         <f aca="false">SUMIF(E6:E13,"Pass-through",D6:D13)</f>
@@ -4308,7 +4354,7 @@
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C19" s="29"/>
       <c r="D19" s="29"/>
@@ -4345,28 +4391,28 @@
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="23" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">Assumptions!$C$6</f>
@@ -4379,7 +4425,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">Assumptions!$C$79</f>
@@ -4392,7 +4438,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">Assumptions!$C$80</f>
@@ -4405,7 +4451,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C9" s="8" t="n">
         <f aca="false">Assumptions!$C$81</f>
@@ -4418,7 +4464,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C10" s="8" t="n">
         <f aca="false">Assumptions!$C$82</f>
@@ -4431,7 +4477,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="8" t="n">
         <f aca="false">Assumptions!$C$83</f>
@@ -4444,7 +4490,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12" s="8" t="n">
         <f aca="false">Assumptions!$C$84</f>
@@ -4457,7 +4503,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="8" t="n">
         <f aca="false">Assumptions!$C$85</f>
@@ -4470,7 +4516,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C14" s="8" t="n">
         <f aca="false">Assumptions!$C$86</f>
@@ -4483,7 +4529,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C15" s="8" t="n">
         <f aca="false">Assumptions!$C$87</f>
@@ -4496,7 +4542,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C16" s="8" t="n">
         <f aca="false">Assumptions!$C$88</f>
@@ -4509,7 +4555,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C17" s="8" t="n">
         <f aca="false">Assumptions!$C$89</f>
@@ -4522,7 +4568,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C18" s="8" t="n">
         <f aca="false">Assumptions!$C$90</f>
@@ -4535,7 +4581,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C19" s="28" t="n">
         <f aca="false">SUM(C6:C18)</f>
@@ -4547,7 +4593,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C21" s="13" t="n">
         <f aca="false">C6</f>
@@ -4556,7 +4602,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C22" s="13" t="n">
         <f aca="false">C19-C6</f>
@@ -4580,7 +4626,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:E25"/>
+  <dimension ref="B1:E26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.5"/>
@@ -4591,28 +4637,28 @@
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C6" s="33" t="n">
         <f aca="false">Assumptions!$C$65</f>
@@ -4621,31 +4667,31 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C7" s="13" t="n">
         <f aca="false">C6*Assumptions!$C$66</f>
         <v>94500000</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">-Assumptions!$C$11</f>
         <v>-73600000</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="35" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C9" s="36" t="n">
         <f aca="false">C7+C8</f>
@@ -4654,91 +4700,91 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C11" s="8" t="n">
         <f aca="false">-Assumptions!$C$67</f>
         <v>-3500000</v>
       </c>
       <c r="D11" s="37" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C12" s="8" t="n">
         <f aca="false">-Assumptions!$C$68</f>
         <v>-2000000</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C13" s="8" t="n">
         <f aca="false">-Assumptions!$C$69</f>
         <v>-3500000</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C14" s="8" t="n">
         <f aca="false">-Assumptions!$C$70</f>
         <v>-2000000</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" s="8" t="n">
         <f aca="false">-Assumptions!$C$71</f>
         <v>-500000</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C16" s="8" t="n">
         <f aca="false">-Assumptions!$C$72</f>
         <v>-1500000</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C17" s="8" t="n">
         <f aca="false">-Assumptions!$C$73</f>
         <v>-800000</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C18" s="13" t="n">
         <f aca="false">SUM(C11:C17)</f>
@@ -4747,48 +4793,57 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C20" s="13" t="n">
         <f aca="false">-C7*Assumptions!$C$74</f>
-        <v>-2835000</v>
+        <v>-4725000</v>
       </c>
       <c r="D20" s="34" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C21" s="13" t="n">
         <f aca="false">-C7*(Assumptions!$C$75+Assumptions!$C$76)</f>
         <v>-4063500</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="35" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C23" s="36" t="n">
         <f aca="false">C9+C18+C20+C21</f>
-        <v>201500</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
+        <v>-1688500</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="C24" s="39" t="str">
+        <f aca="false">IF(C23&gt;0,C23,"฿0 — no profit to transfer at this fee/cost rate")</f>
+        <v>฿0 — no profit to transfer at this fee/cost rate</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4805,7 +4860,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:H24"/>
+  <dimension ref="B1:H25"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.5"/>
@@ -4816,40 +4871,40 @@
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -4859,8 +4914,8 @@
       <c r="H6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="38" t="s">
-        <v>172</v>
+      <c r="B7" s="40" t="s">
+        <v>174</v>
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">Assumptions!$C$19*Assumptions!$C$24*12</f>
@@ -4884,8 +4939,8 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="38" t="s">
-        <v>173</v>
+      <c r="B8" s="40" t="s">
+        <v>175</v>
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">Assumptions!$C$20*Assumptions!$C$25</f>
@@ -4909,8 +4964,8 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="38" t="s">
-        <v>174</v>
+      <c r="B9" s="40" t="s">
+        <v>176</v>
       </c>
       <c r="C9" s="8" t="n">
         <f aca="false">Assumptions!$C$20*Assumptions!$C$26*Assumptions!$C$27</f>
@@ -4934,8 +4989,8 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="38" t="s">
-        <v>71</v>
+      <c r="B10" s="40" t="s">
+        <v>72</v>
       </c>
       <c r="C10" s="8" t="n">
         <f aca="false">Assumptions!$C$32</f>
@@ -4959,8 +5014,8 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="38" t="s">
-        <v>72</v>
+      <c r="B11" s="40" t="s">
+        <v>73</v>
       </c>
       <c r="C11" s="8" t="n">
         <f aca="false">Assumptions!$C$33</f>
@@ -4984,231 +5039,259 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="C12" s="28" t="n">
-        <f aca="false">SUM(C7:C11)</f>
+      <c r="B12" s="40" t="s">
+        <v>177</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <f aca="false">MAX(IFERROR('32-rai Economics'!$C$23*((Assumptions!$C$55)-(0))/Assumptions!$G$55,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <f aca="false">MAX(IFERROR('32-rai Economics'!$C$23*((Assumptions!$D$55)-(Assumptions!$C$55))/Assumptions!$G$55,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <f aca="false">MAX(IFERROR('32-rai Economics'!$C$23*((Assumptions!$E$55)-(Assumptions!$D$55))/Assumptions!$G$55,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <f aca="false">MAX(IFERROR('32-rai Economics'!$C$23*((Assumptions!$F$55)-(Assumptions!$E$55))/Assumptions!$G$55,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <f aca="false">MAX(IFERROR('32-rai Economics'!$C$23*((Assumptions!$G$55)-(Assumptions!$F$55))/Assumptions!$G$55,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="C13" s="28" t="n">
+        <f aca="false">SUM(C7:C12)</f>
         <v>5580000</v>
       </c>
-      <c r="D12" s="28" t="n">
-        <f aca="false">SUM(D7:D11)</f>
+      <c r="D13" s="28" t="n">
+        <f aca="false">SUM(D7:D12)</f>
         <v>8100000</v>
       </c>
-      <c r="E12" s="28" t="n">
-        <f aca="false">SUM(E7:E11)</f>
+      <c r="E13" s="28" t="n">
+        <f aca="false">SUM(E7:E12)</f>
         <v>10320000</v>
       </c>
-      <c r="F12" s="28" t="n">
-        <f aca="false">SUM(F7:F11)</f>
+      <c r="F13" s="28" t="n">
+        <f aca="false">SUM(F7:F12)</f>
         <v>12080000</v>
       </c>
-      <c r="G12" s="28" t="n">
-        <f aca="false">SUM(G7:G11)</f>
+      <c r="G13" s="28" t="n">
+        <f aca="false">SUM(G7:G12)</f>
         <v>13440000</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="C15" s="8" t="n">
+    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="C16" s="8" t="n">
         <f aca="false">Assumptions!$C$34</f>
         <v>3200000</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D16" s="8" t="n">
         <f aca="false">Assumptions!$D$34</f>
         <v>3600000</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E16" s="8" t="n">
         <f aca="false">Assumptions!$E$34</f>
         <v>4000000</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F16" s="8" t="n">
         <f aca="false">Assumptions!$F$34</f>
         <v>4300000</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="G16" s="8" t="n">
         <f aca="false">Assumptions!$G$34</f>
         <v>4600000</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="8" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="8" t="n">
         <f aca="false">Assumptions!$C$35</f>
         <v>600000</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D17" s="8" t="n">
         <f aca="false">Assumptions!$D$35</f>
         <v>900000</v>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="E17" s="8" t="n">
         <f aca="false">Assumptions!$E$35</f>
         <v>1200000</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F17" s="8" t="n">
         <f aca="false">Assumptions!$F$35</f>
         <v>1400000</v>
       </c>
-      <c r="G16" s="8" t="n">
+      <c r="G17" s="8" t="n">
         <f aca="false">Assumptions!$G$35</f>
         <v>1600000</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="C17" s="8" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="C18" s="8" t="n">
         <f aca="false">Assumptions!$C$19*Assumptions!$C$28*12</f>
         <v>810000</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D18" s="8" t="n">
         <f aca="false">Assumptions!$D$19*Assumptions!$C$28*12</f>
         <v>1188000</v>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E18" s="8" t="n">
         <f aca="false">Assumptions!$E$19*Assumptions!$C$28*12</f>
         <v>1512000</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F18" s="8" t="n">
         <f aca="false">Assumptions!$F$19*Assumptions!$C$28*12</f>
         <v>1728000</v>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="G18" s="8" t="n">
         <f aca="false">Assumptions!$G$19*Assumptions!$C$28*12</f>
         <v>1890000</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="8" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="8" t="n">
         <f aca="false">Assumptions!$C$36</f>
         <v>350000</v>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D19" s="8" t="n">
         <f aca="false">Assumptions!$D$36</f>
         <v>400000</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="E19" s="8" t="n">
         <f aca="false">Assumptions!$E$36</f>
         <v>450000</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F19" s="8" t="n">
         <f aca="false">Assumptions!$F$36</f>
         <v>480000</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G19" s="8" t="n">
         <f aca="false">Assumptions!$G$36</f>
         <v>500000</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="8" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="8" t="n">
         <f aca="false">Assumptions!$C$37</f>
         <v>300000</v>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D20" s="8" t="n">
         <f aca="false">Assumptions!$D$37</f>
         <v>320000</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E20" s="8" t="n">
         <f aca="false">Assumptions!$E$37</f>
         <v>340000</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F20" s="8" t="n">
         <f aca="false">Assumptions!$F$37</f>
         <v>360000</v>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="G20" s="8" t="n">
         <f aca="false">Assumptions!$G$37</f>
         <v>380000</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="C20" s="28" t="n">
-        <f aca="false">SUM(C15:C19)</f>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="C21" s="28" t="n">
+        <f aca="false">SUM(C16:C20)</f>
         <v>5260000</v>
       </c>
-      <c r="D20" s="28" t="n">
-        <f aca="false">SUM(D15:D19)</f>
+      <c r="D21" s="28" t="n">
+        <f aca="false">SUM(D16:D20)</f>
         <v>6408000</v>
       </c>
-      <c r="E20" s="28" t="n">
-        <f aca="false">SUM(E15:E19)</f>
+      <c r="E21" s="28" t="n">
+        <f aca="false">SUM(E16:E20)</f>
         <v>7502000</v>
       </c>
-      <c r="F20" s="28" t="n">
-        <f aca="false">SUM(F15:F19)</f>
+      <c r="F21" s="28" t="n">
+        <f aca="false">SUM(F16:F20)</f>
         <v>8268000</v>
       </c>
-      <c r="G20" s="28" t="n">
-        <f aca="false">SUM(G15:G19)</f>
+      <c r="G21" s="28" t="n">
+        <f aca="false">SUM(G16:G20)</f>
         <v>8970000</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="C22" s="28" t="n">
-        <f aca="false">C12-C20</f>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="C23" s="28" t="n">
+        <f aca="false">C13-C21</f>
         <v>320000</v>
       </c>
-      <c r="D22" s="28" t="n">
-        <f aca="false">D12-D20</f>
+      <c r="D23" s="28" t="n">
+        <f aca="false">D13-D21</f>
         <v>1692000</v>
       </c>
-      <c r="E22" s="28" t="n">
-        <f aca="false">E12-E20</f>
+      <c r="E23" s="28" t="n">
+        <f aca="false">E13-E21</f>
         <v>2818000</v>
       </c>
-      <c r="F22" s="28" t="n">
-        <f aca="false">F12-F20</f>
+      <c r="F23" s="28" t="n">
+        <f aca="false">F13-F21</f>
         <v>3812000</v>
       </c>
-      <c r="G22" s="28" t="n">
-        <f aca="false">G12-G20</f>
+      <c r="G23" s="28" t="n">
+        <f aca="false">G13-G21</f>
         <v>4470000</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
+    <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B25:G25"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5237,40 +5320,40 @@
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="20"/>
@@ -5280,8 +5363,8 @@
       <c r="H6" s="20"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="38" t="s">
-        <v>184</v>
+      <c r="B7" s="40" t="s">
+        <v>188</v>
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">Assumptions!$C$40*Assumptions!$C$43*Assumptions!$C$41*365</f>
@@ -5305,8 +5388,8 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="38" t="s">
-        <v>185</v>
+      <c r="B8" s="40" t="s">
+        <v>189</v>
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">Assumptions!$C$44*Assumptions!$C$47*Assumptions!$C$45*365</f>
@@ -5330,8 +5413,8 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="38" t="s">
-        <v>186</v>
+      <c r="B9" s="40" t="s">
+        <v>190</v>
       </c>
       <c r="C9" s="8" t="n">
         <f aca="false">Assumptions!$C$48*Assumptions!$C$51*Assumptions!$C$49*365</f>
@@ -5355,8 +5438,8 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="38" t="s">
-        <v>187</v>
+      <c r="B10" s="40" t="s">
+        <v>191</v>
       </c>
       <c r="C10" s="8" t="n">
         <f aca="false">Assumptions!$C$20*Assumptions!$C$56+Assumptions!$C$55*Assumptions!$C$57</f>
@@ -5380,8 +5463,8 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="38" t="s">
-        <v>188</v>
+      <c r="B11" s="40" t="s">
+        <v>192</v>
       </c>
       <c r="C11" s="8" t="n">
         <f aca="false">Assumptions!$C$55*Assumptions!$C$58</f>
@@ -5406,7 +5489,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="35" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C12" s="36" t="n">
         <f aca="false">SUM(C7:C11)</f>
@@ -5431,7 +5514,7 @@
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="20" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
@@ -5441,8 +5524,8 @@
       <c r="H14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="38" t="s">
-        <v>189</v>
+      <c r="B15" s="40" t="s">
+        <v>193</v>
       </c>
       <c r="C15" s="8" t="n">
         <f aca="false">Assumptions!$C$59</f>
@@ -5466,8 +5549,8 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="38" t="s">
-        <v>190</v>
+      <c r="B16" s="40" t="s">
+        <v>194</v>
       </c>
       <c r="C16" s="8" t="n">
         <f aca="false">Assumptions!$C$60</f>
@@ -5492,7 +5575,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="35" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C17" s="36" t="n">
         <f aca="false">SUM(C15:C16)</f>
@@ -5517,7 +5600,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="35" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C19" s="36" t="n">
         <f aca="false">C12-C17</f>
@@ -5571,40 +5654,40 @@
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">-'Sanctuary Capex'!C19</f>
@@ -5628,35 +5711,35 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="8" t="n">
-        <f aca="false">'Sanctuary P&amp;L'!C22+'Community P&amp;L'!C19</f>
+        <f aca="false">'Sanctuary P&amp;L'!C23+'Community P&amp;L'!C19</f>
         <v>341800</v>
       </c>
       <c r="E7" s="8" t="n">
-        <f aca="false">'Sanctuary P&amp;L'!D22+'Community P&amp;L'!D19</f>
+        <f aca="false">'Sanctuary P&amp;L'!D23+'Community P&amp;L'!D19</f>
         <v>2175240</v>
       </c>
       <c r="F7" s="8" t="n">
-        <f aca="false">'Sanctuary P&amp;L'!E22+'Community P&amp;L'!E19</f>
+        <f aca="false">'Sanctuary P&amp;L'!E23+'Community P&amp;L'!E19</f>
         <v>3721000</v>
       </c>
       <c r="G7" s="8" t="n">
-        <f aca="false">'Sanctuary P&amp;L'!F22+'Community P&amp;L'!F19</f>
+        <f aca="false">'Sanctuary P&amp;L'!F23+'Community P&amp;L'!F19</f>
         <v>4902400</v>
       </c>
       <c r="H7" s="8" t="n">
-        <f aca="false">'Sanctuary P&amp;L'!G22+'Community P&amp;L'!G19</f>
+        <f aca="false">'Sanctuary P&amp;L'!G23+'Community P&amp;L'!G19</f>
         <v>5601360</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C8" s="28" t="n">
         <f aca="false">C6+C7</f>
@@ -5685,7 +5768,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="36" t="n">
         <f aca="false">C8</f>
@@ -5714,12 +5797,12 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="34" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="34" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/business-plan/model/Angel_Arms_Financial_Model.xlsx
+++ b/business-plan/model/Angel_Arms_Financial_Model.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="208">
   <si>
     <t xml:space="preserve">Angel Arms Horse Sanctuary — Financial Model</t>
   </si>
@@ -117,7 +117,10 @@
     <t xml:space="preserve">32-rai land (owner-financed, not yours)</t>
   </si>
   <si>
-    <t xml:space="preserve">32-rai infrastructure (your exposure)</t>
+    <t xml:space="preserve">32-rai infrastructure — charged to plot-sale proceeds (capped)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32-rai infrastructure — funded by donations</t>
   </si>
   <si>
     <t xml:space="preserve">32-rai profit transferred to Sanctuary (5-yr total)</t>
@@ -360,6 +363,12 @@
     <t xml:space="preserve">Specific Business Tax — SBT (% of sale revenue, est.)</t>
   </si>
   <si>
+    <t xml:space="preserve">Infrastructure charged to plot-sale proceeds (cap, THB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost above this cap is assumed donation-funded, not deducted from plot-sale profit</t>
+  </si>
+  <si>
     <t xml:space="preserve">SANCTUARY CAPEX (10 rai)</t>
   </si>
   <si>
@@ -522,7 +531,13 @@
     <t xml:space="preserve">Flood-proof floating villa capex</t>
   </si>
   <si>
-    <t xml:space="preserve">Subtotal infrastructure</t>
+    <t xml:space="preserve">Subtotal infrastructure (full cost)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  of which charged to plot-sale proceeds (capped)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  of which funded by donations (external)</t>
   </si>
   <si>
     <t xml:space="preserve">Agent fee (on sale)</t>
@@ -540,7 +555,7 @@
     <t xml:space="preserve">  → transferred to the Sanctuary as revenue (see Sanctuary P&amp;L)</t>
   </si>
   <si>
-    <t xml:space="preserve">This piece is designed to roughly break even — it's a community-building tool, not a profit engine. Your real exposure is the infrastructure subtotal above, ideally funded from buyer deposits.</t>
+    <t xml:space="preserve">Infrastructure cost above the cap is assumed donation-funded rather than deducted from plot-sale proceeds — confirm that donor commitment is real before relying on this margin. Your capital exposure here is just the capped amount, ideally funded from buyer deposits.</t>
   </si>
   <si>
     <t xml:space="preserve">Sanctuary 5-Year Operating Plan</t>
@@ -812,7 +827,7 @@
       <b val="true"/>
       <i val="true"/>
       <sz val="9.5"/>
-      <color rgb="FFC24A78"/>
+      <color rgb="FF2F6B45"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1047,7 +1062,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1064,6 +1079,19 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <i val="1"/>
+        <color rgb="FFC24A78"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1211,7 +1239,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Summary!$C$19:$H$19</c:f>
+              <c:f>Summary!$C$20:$H$20</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -1237,7 +1265,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Summary!$C$20:$H$20</c:f>
+              <c:f>Summary!$C$21:$H$21</c:f>
               <c:numCache>
                 <c:formatCode>\฿#,##0;"(฿"#,##0\);\-</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1245,13 +1273,13 @@
                   <c:v>-54700000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>341800</c:v>
+                  <c:v>3758612.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2175240</c:v>
+                  <c:v>5022583.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3721000</c:v>
+                  <c:v>6568343.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>4902400</c:v>
@@ -1265,8 +1293,8 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="43464265"/>
-        <c:axId val="51536404"/>
+        <c:axId val="32878716"/>
+        <c:axId val="56302612"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -1321,7 +1349,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Summary!$C$19:$H$19</c:f>
+              <c:f>Summary!$C$20:$H$20</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -1347,7 +1375,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Summary!$C$21:$H$21</c:f>
+              <c:f>Summary!$C$22:$H$22</c:f>
               <c:numCache>
                 <c:formatCode>\฿#,##0;"(฿"#,##0\);\-</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1355,19 +1383,19 @@
                   <c:v>-54700000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-54358200</c:v>
+                  <c:v>-50941387.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-52182960</c:v>
+                  <c:v>-45918803.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-48461960</c:v>
+                  <c:v>-39350460</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-43559560</c:v>
+                  <c:v>-34448060</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-37958200</c:v>
+                  <c:v>-28846700</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1382,11 +1410,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="43464265"/>
-        <c:axId val="51536404"/>
+        <c:axId val="32878716"/>
+        <c:axId val="56302612"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="43464265"/>
+        <c:axId val="32878716"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1418,7 +1446,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51536404"/>
+        <c:crossAx val="56302612"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1426,7 +1454,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="51536404"/>
+        <c:axId val="56302612"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1502,7 +1530,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43464265"/>
+        <c:crossAx val="32878716"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1713,11 +1741,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="82041251"/>
-        <c:axId val="35534150"/>
+        <c:axId val="50198525"/>
+        <c:axId val="10841163"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="82041251"/>
+        <c:axId val="50198525"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1749,7 +1777,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35534150"/>
+        <c:crossAx val="10841163"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1757,7 +1785,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="35534150"/>
+        <c:axId val="10841163"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1799,7 +1827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82041251"/>
+        <c:crossAx val="50198525"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1949,13 +1977,13 @@
                 <c:formatCode>\฿#,##0;"(฿"#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>320000</c:v>
+                  <c:v>3736812.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1692000</c:v>
+                  <c:v>4539343.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2818000</c:v>
+                  <c:v>5665343.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>3812000</c:v>
@@ -1976,11 +2004,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="2054398"/>
-        <c:axId val="17340756"/>
+        <c:axId val="63158731"/>
+        <c:axId val="41245951"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="2054398"/>
+        <c:axId val="63158731"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2012,7 +2040,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17340756"/>
+        <c:crossAx val="41245951"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2020,7 +2048,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="17340756"/>
+        <c:axId val="41245951"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2062,7 +2090,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2054398"/>
+        <c:crossAx val="63158731"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2208,13 +2236,13 @@
                   <c:v>-54700000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>341800</c:v>
+                  <c:v>3758612.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2175240</c:v>
+                  <c:v>5022583.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3721000</c:v>
+                  <c:v>6568343.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>4902400</c:v>
@@ -2228,8 +2256,8 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="68199892"/>
-        <c:axId val="25305814"/>
+        <c:axId val="47119816"/>
+        <c:axId val="80589935"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2318,19 +2346,19 @@
                   <c:v>-54700000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-54358200</c:v>
+                  <c:v>-50941387.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-52182960</c:v>
+                  <c:v>-45918803.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-48461960</c:v>
+                  <c:v>-39350460</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-43559560</c:v>
+                  <c:v>-34448060</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-37958200</c:v>
+                  <c:v>-28846700</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2345,11 +2373,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="68199892"/>
-        <c:axId val="25305814"/>
+        <c:axId val="47119816"/>
+        <c:axId val="80589935"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="68199892"/>
+        <c:axId val="47119816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2381,7 +2409,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25305814"/>
+        <c:crossAx val="80589935"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2389,7 +2417,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="25305814"/>
+        <c:axId val="80589935"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2465,7 +2493,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68199892"/>
+        <c:crossAx val="47119816"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2499,13 +2527,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>101160</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>100800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>638640</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>81000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -2514,7 +2542,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="222120" y="4152960"/>
+        <a:off x="222120" y="4343400"/>
         <a:ext cx="8639640" cy="3599640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2938,7 +2966,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:H46"/>
+  <dimension ref="B1:H47"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.5"/>
@@ -3017,8 +3045,8 @@
         <v>29</v>
       </c>
       <c r="C12" s="8" t="n">
-        <f aca="false">'32-rai Economics'!C18</f>
-        <v>-13800000</v>
+        <f aca="false">'32-rai Economics'!C19</f>
+        <v>-3000000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3026,8 +3054,8 @@
         <v>30</v>
       </c>
       <c r="C13" s="8" t="n">
-        <f aca="false">SUM('Sanctuary P&amp;L'!C12:G12)</f>
-        <v>0</v>
+        <f aca="false">'32-rai Economics'!C20</f>
+        <v>10800000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3035,8 +3063,8 @@
         <v>31</v>
       </c>
       <c r="C14" s="8" t="n">
-        <f aca="false">'Cash Flow'!D8</f>
-        <v>341800</v>
+        <f aca="false">SUM('Sanctuary P&amp;L'!C12:G12)</f>
+        <v>9111500</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3044,8 +3072,8 @@
         <v>32</v>
       </c>
       <c r="C15" s="8" t="n">
-        <f aca="false">'Cash Flow'!H8</f>
-        <v>5601360</v>
+        <f aca="false">'Cash Flow'!D8</f>
+        <v>3758612.5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3053,111 +3081,115 @@
         <v>33</v>
       </c>
       <c r="C16" s="8" t="n">
+        <f aca="false">'Cash Flow'!H8</f>
+        <v>5601360</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="8" t="n">
         <f aca="false">'Cash Flow'!H9</f>
-        <v>-37958200</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="9" t="s">
+        <v>-28846700</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="10" t="str">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="10" t="str">
         <f aca="false">'Cash Flow'!C5</f>
         <v>Year 0 (capital)</v>
       </c>
-      <c r="D19" s="10" t="str">
+      <c r="D20" s="10" t="str">
         <f aca="false">'Cash Flow'!D5</f>
         <v>Year 1</v>
       </c>
-      <c r="E19" s="10" t="str">
+      <c r="E20" s="10" t="str">
         <f aca="false">'Cash Flow'!E5</f>
         <v>Year 2</v>
       </c>
-      <c r="F19" s="10" t="str">
+      <c r="F20" s="10" t="str">
         <f aca="false">'Cash Flow'!F5</f>
         <v>Year 3</v>
       </c>
-      <c r="G19" s="10" t="str">
+      <c r="G20" s="10" t="str">
         <f aca="false">'Cash Flow'!G5</f>
         <v>Year 4</v>
       </c>
-      <c r="H19" s="10" t="str">
+      <c r="H20" s="10" t="str">
         <f aca="false">'Cash Flow'!H5</f>
         <v>Year 5</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="8" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="8" t="n">
         <f aca="false">'Cash Flow'!C8</f>
         <v>-54700000</v>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D21" s="8" t="n">
         <f aca="false">'Cash Flow'!D8</f>
-        <v>341800</v>
-      </c>
-      <c r="E20" s="8" t="n">
+        <v>3758612.5</v>
+      </c>
+      <c r="E21" s="8" t="n">
         <f aca="false">'Cash Flow'!E8</f>
-        <v>2175240</v>
-      </c>
-      <c r="F20" s="8" t="n">
+        <v>5022583.75</v>
+      </c>
+      <c r="F21" s="8" t="n">
         <f aca="false">'Cash Flow'!F8</f>
-        <v>3721000</v>
-      </c>
-      <c r="G20" s="8" t="n">
+        <v>6568343.75</v>
+      </c>
+      <c r="G21" s="8" t="n">
         <f aca="false">'Cash Flow'!G8</f>
         <v>4902400</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H21" s="8" t="n">
         <f aca="false">'Cash Flow'!H8</f>
         <v>5601360</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="8" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="8" t="n">
         <f aca="false">'Cash Flow'!C9</f>
         <v>-54700000</v>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D22" s="8" t="n">
         <f aca="false">'Cash Flow'!D9</f>
-        <v>-54358200</v>
-      </c>
-      <c r="E21" s="8" t="n">
+        <v>-50941387.5</v>
+      </c>
+      <c r="E22" s="8" t="n">
         <f aca="false">'Cash Flow'!E9</f>
-        <v>-52182960</v>
-      </c>
-      <c r="F21" s="8" t="n">
+        <v>-45918803.75</v>
+      </c>
+      <c r="F22" s="8" t="n">
         <f aca="false">'Cash Flow'!F9</f>
-        <v>-48461960</v>
-      </c>
-      <c r="G21" s="8" t="n">
+        <v>-39350460</v>
+      </c>
+      <c r="G22" s="8" t="n">
         <f aca="false">'Cash Flow'!G9</f>
-        <v>-43559560</v>
-      </c>
-      <c r="H21" s="8" t="n">
+        <v>-34448060</v>
+      </c>
+      <c r="H22" s="8" t="n">
         <f aca="false">'Cash Flow'!H9</f>
-        <v>-37958200</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="11" t="s">
-        <v>38</v>
+        <v>-28846700</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3165,10 +3197,15 @@
         <v>39</v>
       </c>
     </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B19:H19"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3186,7 +3223,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:H90"/>
+  <dimension ref="B1:H91"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.5"/>
@@ -3197,17 +3234,17 @@
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -3218,7 +3255,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>23000000</v>
@@ -3226,7 +3263,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>6000000</v>
@@ -3234,7 +3271,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8" s="13" t="n">
         <f aca="false">C6-C7</f>
@@ -3243,7 +3280,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" s="14" t="n">
         <v>46296</v>
@@ -3251,7 +3288,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10" s="14" t="n">
         <v>46478</v>
@@ -3259,7 +3296,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>73600000</v>
@@ -3267,7 +3304,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" s="15" t="n">
         <v>6</v>
@@ -3275,7 +3312,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" s="13" t="n">
         <f aca="false">C11/C12</f>
@@ -3284,7 +3321,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>46569</v>
@@ -3292,7 +3329,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C15" s="16" t="n">
         <v>3</v>
@@ -3300,7 +3337,7 @@
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -3311,30 +3348,30 @@
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C19" s="15" t="n">
         <v>15</v>
@@ -3354,7 +3391,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C20" s="15" t="n">
         <v>2000</v>
@@ -3374,7 +3411,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C21" s="16" t="n">
         <v>120</v>
@@ -3394,7 +3431,7 @@
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -3405,7 +3442,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24" s="12" t="n">
         <v>15000</v>
@@ -3413,7 +3450,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C25" s="18" t="n">
         <v>300</v>
@@ -3421,7 +3458,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C26" s="19" t="n">
         <v>0.2</v>
@@ -3429,7 +3466,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C27" s="18" t="n">
         <v>700</v>
@@ -3437,18 +3474,18 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C28" s="18" t="n">
         <v>4500</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -3459,30 +3496,30 @@
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C32" s="18" t="n">
         <v>1200000</v>
@@ -3502,7 +3539,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C33" s="18" t="n">
         <v>800000</v>
@@ -3522,7 +3559,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C34" s="18" t="n">
         <v>3200000</v>
@@ -3542,7 +3579,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C35" s="18" t="n">
         <v>600000</v>
@@ -3562,7 +3599,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C36" s="18" t="n">
         <v>350000</v>
@@ -3582,7 +3619,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C37" s="18" t="n">
         <v>300000</v>
@@ -3602,7 +3639,7 @@
     </row>
     <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C39" s="20"/>
       <c r="D39" s="20"/>
@@ -3613,7 +3650,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C40" s="16" t="n">
         <v>3</v>
@@ -3621,7 +3658,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C41" s="18" t="n">
         <v>2500</v>
@@ -3629,30 +3666,30 @@
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C43" s="19" t="n">
         <v>0.15</v>
@@ -3672,7 +3709,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C44" s="16" t="n">
         <v>4</v>
@@ -3680,7 +3717,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C45" s="18" t="n">
         <v>800</v>
@@ -3688,30 +3725,30 @@
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C47" s="19" t="n">
         <v>0.1</v>
@@ -3731,7 +3768,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C48" s="16" t="n">
         <v>1</v>
@@ -3739,7 +3776,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C49" s="18" t="n">
         <v>4500</v>
@@ -3747,30 +3784,30 @@
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C51" s="19" t="n">
         <v>0.15</v>
@@ -3790,7 +3827,7 @@
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C53" s="20"/>
       <c r="D53" s="20"/>
@@ -3801,30 +3838,30 @@
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F54" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C55" s="15" t="n">
         <v>6</v>
@@ -3844,7 +3881,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C56" s="18" t="n">
         <v>60</v>
@@ -3852,7 +3889,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C57" s="18" t="n">
         <v>8000</v>
@@ -3860,7 +3897,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C58" s="12" t="n">
         <v>30000</v>
@@ -3868,7 +3905,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C59" s="18" t="n">
         <v>900000</v>
@@ -3888,7 +3925,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C60" s="18" t="n">
         <v>200000</v>
@@ -3908,7 +3945,7 @@
     </row>
     <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C62" s="20"/>
       <c r="D62" s="20"/>
@@ -3919,7 +3956,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C63" s="16" t="n">
         <v>32</v>
@@ -3927,7 +3964,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C64" s="15" t="n">
         <v>5</v>
@@ -3935,7 +3972,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C65" s="21" t="n">
         <f aca="false">C63-C64</f>
@@ -3944,7 +3981,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C66" s="12" t="n">
         <v>3500000</v>
@@ -3952,7 +3989,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C67" s="18" t="n">
         <v>3500000</v>
@@ -3960,7 +3997,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C68" s="18" t="n">
         <v>2000000</v>
@@ -3968,7 +4005,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C69" s="18" t="n">
         <v>3500000</v>
@@ -3976,7 +4013,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C70" s="18" t="n">
         <v>2000000</v>
@@ -3984,7 +4021,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C71" s="18" t="n">
         <v>500000</v>
@@ -3992,7 +4029,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C72" s="18" t="n">
         <v>1500000</v>
@@ -4000,7 +4037,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C73" s="18" t="n">
         <v>800000</v>
@@ -4008,7 +4045,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C74" s="22" t="n">
         <v>0.05</v>
@@ -4016,7 +4053,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C75" s="19" t="n">
         <v>0.01</v>
@@ -4024,74 +4061,77 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C76" s="22" t="n">
         <v>0.033</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B78" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C78" s="5"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
-      <c r="G78" s="5"/>
-      <c r="H78" s="5"/>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="6" t="s">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="C79" s="18" t="n">
-        <v>13000000</v>
-      </c>
+      <c r="C77" s="12" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="H77" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B79" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C80" s="18" t="n">
-        <v>4500000</v>
+        <v>13000000</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C81" s="18" t="n">
-        <v>2900000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C82" s="18" t="n">
-        <v>2500000</v>
+        <v>2900000</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C83" s="18" t="n">
-        <v>1800000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C84" s="18" t="n">
-        <v>1500000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C85" s="18" t="n">
         <v>1500000</v>
@@ -4099,41 +4139,49 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C86" s="18" t="n">
-        <v>1200000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C87" s="18" t="n">
-        <v>900000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C88" s="18" t="n">
-        <v>800000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C89" s="18" t="n">
-        <v>600000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C90" s="18" t="n">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B91" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C91" s="18" t="n">
         <v>500000</v>
       </c>
     </row>
@@ -4146,7 +4194,7 @@
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B53:H53"/>
     <mergeCell ref="B62:H62"/>
-    <mergeCell ref="B78:H78"/>
+    <mergeCell ref="B79:H79"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4175,26 +4223,26 @@
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="23" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4203,14 +4251,14 @@
         <v>46296</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D6" s="8" t="n">
         <f aca="false">Assumptions!$C$7</f>
         <v>6000000</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4219,14 +4267,14 @@
         <v>46478</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D7" s="8" t="n">
         <f aca="false">Assumptions!$C$8</f>
         <v>17000000</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4235,14 +4283,14 @@
         <v>46569</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D8" s="8" t="n">
         <f aca="false">Assumptions!$C$13</f>
         <v>12266666.6666667</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4251,14 +4299,14 @@
         <v>46661</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D9" s="8" t="n">
         <f aca="false">Assumptions!$C$13</f>
         <v>12266666.6666667</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4267,14 +4315,14 @@
         <v>46753</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D10" s="8" t="n">
         <f aca="false">Assumptions!$C$13</f>
         <v>12266666.6666667</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4283,14 +4331,14 @@
         <v>46844</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D11" s="8" t="n">
         <f aca="false">Assumptions!$C$13</f>
         <v>12266666.6666667</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4299,14 +4347,14 @@
         <v>46935</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D12" s="8" t="n">
         <f aca="false">Assumptions!$C$13</f>
         <v>12266666.6666667</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4315,19 +4363,19 @@
         <v>47027</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D13" s="8" t="n">
         <f aca="false">Assumptions!$C$13</f>
         <v>12266666.6666667</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="27" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D15" s="28" t="n">
         <f aca="false">SUM(D6:D13)</f>
@@ -4336,7 +4384,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D16" s="13" t="n">
         <f aca="false">SUMIF(E6:E13,"You",D6:D13)</f>
@@ -4345,7 +4393,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D17" s="13" t="n">
         <f aca="false">SUMIF(E6:E13,"Pass-through",D6:D13)</f>
@@ -4354,7 +4402,7 @@
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C19" s="29"/>
       <c r="D19" s="29"/>
@@ -4391,28 +4439,28 @@
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="23" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">Assumptions!$C$6</f>
@@ -4425,10 +4473,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C7" s="8" t="n">
-        <f aca="false">Assumptions!$C$79</f>
+        <f aca="false">Assumptions!$C$80</f>
         <v>13000000</v>
       </c>
       <c r="D7" s="30" t="n">
@@ -4438,10 +4486,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C8" s="8" t="n">
-        <f aca="false">Assumptions!$C$80</f>
+        <f aca="false">Assumptions!$C$81</f>
         <v>4500000</v>
       </c>
       <c r="D8" s="30" t="n">
@@ -4451,10 +4499,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C9" s="8" t="n">
-        <f aca="false">Assumptions!$C$81</f>
+        <f aca="false">Assumptions!$C$82</f>
         <v>2900000</v>
       </c>
       <c r="D9" s="30" t="n">
@@ -4464,10 +4512,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C10" s="8" t="n">
-        <f aca="false">Assumptions!$C$82</f>
+        <f aca="false">Assumptions!$C$83</f>
         <v>2500000</v>
       </c>
       <c r="D10" s="30" t="n">
@@ -4477,10 +4525,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C11" s="8" t="n">
-        <f aca="false">Assumptions!$C$83</f>
+        <f aca="false">Assumptions!$C$84</f>
         <v>1800000</v>
       </c>
       <c r="D11" s="30" t="n">
@@ -4490,10 +4538,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C12" s="8" t="n">
-        <f aca="false">Assumptions!$C$84</f>
+        <f aca="false">Assumptions!$C$85</f>
         <v>1500000</v>
       </c>
       <c r="D12" s="30" t="n">
@@ -4503,10 +4551,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C13" s="8" t="n">
-        <f aca="false">Assumptions!$C$85</f>
+        <f aca="false">Assumptions!$C$86</f>
         <v>1500000</v>
       </c>
       <c r="D13" s="30" t="n">
@@ -4516,10 +4564,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C14" s="8" t="n">
-        <f aca="false">Assumptions!$C$86</f>
+        <f aca="false">Assumptions!$C$87</f>
         <v>1200000</v>
       </c>
       <c r="D14" s="30" t="n">
@@ -4529,10 +4577,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C15" s="8" t="n">
-        <f aca="false">Assumptions!$C$87</f>
+        <f aca="false">Assumptions!$C$88</f>
         <v>900000</v>
       </c>
       <c r="D15" s="30" t="n">
@@ -4542,10 +4590,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C16" s="8" t="n">
-        <f aca="false">Assumptions!$C$88</f>
+        <f aca="false">Assumptions!$C$89</f>
         <v>800000</v>
       </c>
       <c r="D16" s="30" t="n">
@@ -4555,10 +4603,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C17" s="8" t="n">
-        <f aca="false">Assumptions!$C$89</f>
+        <f aca="false">Assumptions!$C$90</f>
         <v>600000</v>
       </c>
       <c r="D17" s="30" t="n">
@@ -4568,10 +4616,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C18" s="8" t="n">
-        <f aca="false">Assumptions!$C$90</f>
+        <f aca="false">Assumptions!$C$91</f>
         <v>500000</v>
       </c>
       <c r="D18" s="30" t="n">
@@ -4581,7 +4629,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="27" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C19" s="28" t="n">
         <f aca="false">SUM(C6:C18)</f>
@@ -4593,7 +4641,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C21" s="13" t="n">
         <f aca="false">C6</f>
@@ -4602,7 +4650,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C22" s="13" t="n">
         <f aca="false">C19-C6</f>
@@ -4626,7 +4674,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:E26"/>
+  <dimension ref="B1:E28"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.5"/>
@@ -4637,28 +4685,28 @@
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="32" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C6" s="33" t="n">
         <f aca="false">Assumptions!$C$65</f>
@@ -4667,31 +4715,31 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C7" s="13" t="n">
         <f aca="false">C6*Assumptions!$C$66</f>
         <v>94500000</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">-Assumptions!$C$11</f>
         <v>-73600000</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="35" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C9" s="36" t="n">
         <f aca="false">C7+C8</f>
@@ -4700,151 +4748,174 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C11" s="8" t="n">
         <f aca="false">-Assumptions!$C$67</f>
         <v>-3500000</v>
       </c>
       <c r="D11" s="37" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C12" s="8" t="n">
         <f aca="false">-Assumptions!$C$68</f>
         <v>-2000000</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C13" s="8" t="n">
         <f aca="false">-Assumptions!$C$69</f>
         <v>-3500000</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C14" s="8" t="n">
         <f aca="false">-Assumptions!$C$70</f>
         <v>-2000000</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C15" s="8" t="n">
         <f aca="false">-Assumptions!$C$71</f>
         <v>-500000</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C16" s="8" t="n">
         <f aca="false">-Assumptions!$C$72</f>
         <v>-1500000</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C17" s="8" t="n">
         <f aca="false">-Assumptions!$C$73</f>
         <v>-800000</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="9" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C18" s="13" t="n">
         <f aca="false">SUM(C11:C17)</f>
         <v>-13800000</v>
       </c>
     </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <f aca="false">MAX(C18,-Assumptions!$C$77)</f>
+        <v>-3000000</v>
+      </c>
+    </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C20" s="13" t="n">
+        <f aca="false">-(C18-C19)</f>
+        <v>10800000</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C22" s="13" t="n">
         <f aca="false">-C7*Assumptions!$C$74</f>
         <v>-4725000</v>
       </c>
-      <c r="D20" s="34" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C21" s="13" t="n">
+      <c r="D22" s="34" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C23" s="13" t="n">
         <f aca="false">-C7*(Assumptions!$C$75+Assumptions!$C$76)</f>
         <v>-4063500</v>
       </c>
-      <c r="D21" s="34" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="C23" s="36" t="n">
-        <f aca="false">C9+C18+C20+C21</f>
-        <v>-1688500</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="C24" s="39" t="str">
-        <f aca="false">IF(C23&gt;0,C23,"฿0 — no profit to transfer at this fee/cost rate")</f>
-        <v>฿0 — no profit to transfer at this fee/cost rate</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
+      <c r="D23" s="34" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="36" t="n">
+        <f aca="false">C9+C19+C22+C23</f>
+        <v>9111500</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="C26" s="39" t="n">
+        <f aca="false">IF(C25&gt;0,C25,"฿0 — no profit to transfer at this fee/cost rate")</f>
+        <v>9111500</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="29" t="s">
+        <v>175</v>
+      </c>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B28:E28"/>
   </mergeCells>
+  <conditionalFormatting sqref="C26">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>C25&lt;=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4871,40 +4942,40 @@
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -4915,7 +4986,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="40" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">Assumptions!$C$19*Assumptions!$C$24*12</f>
@@ -4940,7 +5011,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="40" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">Assumptions!$C$20*Assumptions!$C$25</f>
@@ -4965,7 +5036,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="40" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C9" s="8" t="n">
         <f aca="false">Assumptions!$C$20*Assumptions!$C$26*Assumptions!$C$27</f>
@@ -4990,7 +5061,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C10" s="8" t="n">
         <f aca="false">Assumptions!$C$32</f>
@@ -5015,7 +5086,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C11" s="8" t="n">
         <f aca="false">Assumptions!$C$33</f>
@@ -5040,47 +5111,47 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="40" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C12" s="8" t="n">
-        <f aca="false">MAX(IFERROR('32-rai Economics'!$C$23*((Assumptions!$C$55)-(0))/Assumptions!$G$55,0),0)</f>
+        <f aca="false">MAX(IFERROR('32-rai Economics'!$C$25*((Assumptions!$C$55)-(0))/Assumptions!$G$55,0),0)</f>
+        <v>3416812.5</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <f aca="false">MAX(IFERROR('32-rai Economics'!$C$25*((Assumptions!$D$55)-(Assumptions!$C$55))/Assumptions!$G$55,0),0)</f>
+        <v>2847343.75</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <f aca="false">MAX(IFERROR('32-rai Economics'!$C$25*((Assumptions!$E$55)-(Assumptions!$D$55))/Assumptions!$G$55,0),0)</f>
+        <v>2847343.75</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <f aca="false">MAX(IFERROR('32-rai Economics'!$C$25*((Assumptions!$F$55)-(Assumptions!$E$55))/Assumptions!$G$55,0),0)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="8" t="n">
-        <f aca="false">MAX(IFERROR('32-rai Economics'!$C$23*((Assumptions!$D$55)-(Assumptions!$C$55))/Assumptions!$G$55,0),0)</f>
+      <c r="G12" s="8" t="n">
+        <f aca="false">MAX(IFERROR('32-rai Economics'!$C$25*((Assumptions!$G$55)-(Assumptions!$F$55))/Assumptions!$G$55,0),0)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="8" t="n">
-        <f aca="false">MAX(IFERROR('32-rai Economics'!$C$23*((Assumptions!$E$55)-(Assumptions!$D$55))/Assumptions!$G$55,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <f aca="false">MAX(IFERROR('32-rai Economics'!$C$23*((Assumptions!$F$55)-(Assumptions!$E$55))/Assumptions!$G$55,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <f aca="false">MAX(IFERROR('32-rai Economics'!$C$23*((Assumptions!$G$55)-(Assumptions!$F$55))/Assumptions!$G$55,0),0)</f>
-        <v>0</v>
-      </c>
       <c r="H12" s="11" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="27" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C13" s="28" t="n">
         <f aca="false">SUM(C7:C12)</f>
-        <v>5580000</v>
+        <v>8996812.5</v>
       </c>
       <c r="D13" s="28" t="n">
         <f aca="false">SUM(D7:D12)</f>
-        <v>8100000</v>
+        <v>10947343.75</v>
       </c>
       <c r="E13" s="28" t="n">
         <f aca="false">SUM(E7:E12)</f>
-        <v>10320000</v>
+        <v>13167343.75</v>
       </c>
       <c r="F13" s="28" t="n">
         <f aca="false">SUM(F7:F12)</f>
@@ -5093,7 +5164,7 @@
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -5104,7 +5175,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="40" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C16" s="8" t="n">
         <f aca="false">Assumptions!$C$34</f>
@@ -5129,7 +5200,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" s="8" t="n">
         <f aca="false">Assumptions!$C$35</f>
@@ -5154,7 +5225,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="40" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C18" s="8" t="n">
         <f aca="false">Assumptions!$C$19*Assumptions!$C$28*12</f>
@@ -5179,7 +5250,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C19" s="8" t="n">
         <f aca="false">Assumptions!$C$36</f>
@@ -5204,7 +5275,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="40" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C20" s="8" t="n">
         <f aca="false">Assumptions!$C$37</f>
@@ -5229,7 +5300,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="27" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C21" s="28" t="n">
         <f aca="false">SUM(C16:C20)</f>
@@ -5254,19 +5325,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="27" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C23" s="28" t="n">
         <f aca="false">C13-C21</f>
-        <v>320000</v>
+        <v>3736812.5</v>
       </c>
       <c r="D23" s="28" t="n">
         <f aca="false">D13-D21</f>
-        <v>1692000</v>
+        <v>4539343.75</v>
       </c>
       <c r="E23" s="28" t="n">
         <f aca="false">E13-E21</f>
-        <v>2818000</v>
+        <v>5665343.75</v>
       </c>
       <c r="F23" s="28" t="n">
         <f aca="false">F13-F21</f>
@@ -5279,7 +5350,7 @@
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C25" s="29"/>
       <c r="D25" s="29"/>
@@ -5320,40 +5391,40 @@
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="20" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="20"/>
@@ -5364,7 +5435,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="40" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">Assumptions!$C$40*Assumptions!$C$43*Assumptions!$C$41*365</f>
@@ -5389,7 +5460,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="40" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">Assumptions!$C$44*Assumptions!$C$47*Assumptions!$C$45*365</f>
@@ -5414,7 +5485,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="40" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C9" s="8" t="n">
         <f aca="false">Assumptions!$C$48*Assumptions!$C$51*Assumptions!$C$49*365</f>
@@ -5439,7 +5510,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="40" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C10" s="8" t="n">
         <f aca="false">Assumptions!$C$20*Assumptions!$C$56+Assumptions!$C$55*Assumptions!$C$57</f>
@@ -5464,7 +5535,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="40" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C11" s="8" t="n">
         <f aca="false">Assumptions!$C$55*Assumptions!$C$58</f>
@@ -5489,7 +5560,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="35" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C12" s="36" t="n">
         <f aca="false">SUM(C7:C11)</f>
@@ -5514,7 +5585,7 @@
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="20" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
@@ -5525,7 +5596,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="40" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C15" s="8" t="n">
         <f aca="false">Assumptions!$C$59</f>
@@ -5550,7 +5621,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="40" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C16" s="8" t="n">
         <f aca="false">Assumptions!$C$60</f>
@@ -5575,7 +5646,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="35" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C17" s="36" t="n">
         <f aca="false">SUM(C15:C16)</f>
@@ -5600,7 +5671,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="35" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C19" s="36" t="n">
         <f aca="false">C12-C17</f>
@@ -5654,40 +5725,40 @@
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">-'Sanctuary Capex'!C19</f>
@@ -5711,22 +5782,22 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="8" t="n">
         <f aca="false">'Sanctuary P&amp;L'!C23+'Community P&amp;L'!C19</f>
-        <v>341800</v>
+        <v>3758612.5</v>
       </c>
       <c r="E7" s="8" t="n">
         <f aca="false">'Sanctuary P&amp;L'!D23+'Community P&amp;L'!D19</f>
-        <v>2175240</v>
+        <v>5022583.75</v>
       </c>
       <c r="F7" s="8" t="n">
         <f aca="false">'Sanctuary P&amp;L'!E23+'Community P&amp;L'!E19</f>
-        <v>3721000</v>
+        <v>6568343.75</v>
       </c>
       <c r="G7" s="8" t="n">
         <f aca="false">'Sanctuary P&amp;L'!F23+'Community P&amp;L'!F19</f>
@@ -5739,7 +5810,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" s="28" t="n">
         <f aca="false">C6+C7</f>
@@ -5747,15 +5818,15 @@
       </c>
       <c r="D8" s="28" t="n">
         <f aca="false">D6+D7</f>
-        <v>341800</v>
+        <v>3758612.5</v>
       </c>
       <c r="E8" s="28" t="n">
         <f aca="false">E6+E7</f>
-        <v>2175240</v>
+        <v>5022583.75</v>
       </c>
       <c r="F8" s="28" t="n">
         <f aca="false">F6+F7</f>
-        <v>3721000</v>
+        <v>6568343.75</v>
       </c>
       <c r="G8" s="28" t="n">
         <f aca="false">G6+G7</f>
@@ -5768,7 +5839,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" s="36" t="n">
         <f aca="false">C8</f>
@@ -5776,33 +5847,33 @@
       </c>
       <c r="D9" s="36" t="n">
         <f aca="false">C9+D8</f>
-        <v>-54358200</v>
+        <v>-50941387.5</v>
       </c>
       <c r="E9" s="36" t="n">
         <f aca="false">D9+E8</f>
-        <v>-52182960</v>
+        <v>-45918803.75</v>
       </c>
       <c r="F9" s="36" t="n">
         <f aca="false">E9+F8</f>
-        <v>-48461960</v>
+        <v>-39350460</v>
       </c>
       <c r="G9" s="36" t="n">
         <f aca="false">F9+G8</f>
-        <v>-43559560</v>
+        <v>-34448060</v>
       </c>
       <c r="H9" s="36" t="n">
         <f aca="false">G9+H8</f>
-        <v>-37958200</v>
+        <v>-28846700</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="34" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="34" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/business-plan/model/Angel_Arms_Financial_Model.xlsx
+++ b/business-plan/model/Angel_Arms_Financial_Model.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="211">
   <si>
     <t xml:space="preserve">Angel Arms Horse Sanctuary — Financial Model</t>
   </si>
@@ -576,6 +576,12 @@
     <t xml:space="preserve">Riding lessons</t>
   </si>
   <si>
+    <t xml:space="preserve">Donation — horse feed sponsorship (Maxwell)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covers the feed/routine care cost below in full — a donor commitment, not fundraised revenue</t>
+  </si>
+  <si>
     <t xml:space="preserve">32-rai development profit share (net of agent fee)</t>
   </si>
   <si>
@@ -594,13 +600,16 @@
     <t xml:space="preserve">Feed / routine care (horses × ฿ /mo × 12)</t>
   </si>
   <si>
+    <t xml:space="preserve">Fully covered by the Maxwell feed-sponsorship donation above — kept here so the true cost stays visible</t>
+  </si>
+  <si>
     <t xml:space="preserve">TOTAL OPERATING COST</t>
   </si>
   <si>
     <t xml:space="preserve">SANCTUARY NET</t>
   </si>
   <si>
-    <t xml:space="preserve">Vet fees are billed and paid directly by the horse owner — not included here as Foundation revenue or cost.</t>
+    <t xml:space="preserve">Vet fees are billed and paid directly by the horse owner — not included here as Foundation revenue or cost. Feed cost is shown in full above but is fully offset by the Maxwell feed-sponsorship donation.</t>
   </si>
   <si>
     <t xml:space="preserve">Community Amenities 5-Year Operating Plan</t>
@@ -1273,19 +1282,19 @@
                   <c:v>-54700000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3758612.5</c:v>
+                  <c:v>4568612.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5022583.75</c:v>
+                  <c:v>6210583.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6568343.75</c:v>
+                  <c:v>8080343.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4902400</c:v>
+                  <c:v>6630400</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5601360</c:v>
+                  <c:v>7491360</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1293,8 +1302,8 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="32878716"/>
-        <c:axId val="56302612"/>
+        <c:axId val="60346967"/>
+        <c:axId val="7962686"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -1383,19 +1392,19 @@
                   <c:v>-54700000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-50941387.5</c:v>
+                  <c:v>-50131387.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-45918803.75</c:v>
+                  <c:v>-43920803.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-39350460</c:v>
+                  <c:v>-35840460</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-34448060</c:v>
+                  <c:v>-29210060</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-28846700</c:v>
+                  <c:v>-21718700</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1410,11 +1419,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="32878716"/>
-        <c:axId val="56302612"/>
+        <c:axId val="60346967"/>
+        <c:axId val="7962686"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="32878716"/>
+        <c:axId val="60346967"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1446,7 +1455,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56302612"/>
+        <c:crossAx val="7962686"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1454,7 +1463,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="56302612"/>
+        <c:axId val="7962686"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1530,7 +1539,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32878716"/>
+        <c:crossAx val="60346967"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1741,11 +1750,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="50198525"/>
-        <c:axId val="10841163"/>
+        <c:axId val="83682299"/>
+        <c:axId val="62088960"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="50198525"/>
+        <c:axId val="83682299"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1777,7 +1786,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10841163"/>
+        <c:crossAx val="62088960"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1785,7 +1794,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="10841163"/>
+        <c:axId val="62088960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1827,7 +1836,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50198525"/>
+        <c:crossAx val="83682299"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1972,24 +1981,24 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Sanctuary P&amp;L'!$C$23:$G$23</c:f>
+              <c:f>'Sanctuary P&amp;L'!$C$24:$G$24</c:f>
               <c:numCache>
                 <c:formatCode>\฿#,##0;"(฿"#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>3736812.5</c:v>
+                  <c:v>4546812.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4539343.75</c:v>
+                  <c:v>5727343.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5665343.75</c:v>
+                  <c:v>7177343.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3812000</c:v>
+                  <c:v>5540000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4470000</c:v>
+                  <c:v>6360000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2004,11 +2013,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="63158731"/>
-        <c:axId val="41245951"/>
+        <c:axId val="28798824"/>
+        <c:axId val="47955744"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="63158731"/>
+        <c:axId val="28798824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2040,7 +2049,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41245951"/>
+        <c:crossAx val="47955744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2048,7 +2057,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41245951"/>
+        <c:axId val="47955744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2090,7 +2099,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63158731"/>
+        <c:crossAx val="28798824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2236,19 +2245,19 @@
                   <c:v>-54700000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3758612.5</c:v>
+                  <c:v>4568612.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5022583.75</c:v>
+                  <c:v>6210583.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6568343.75</c:v>
+                  <c:v>8080343.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4902400</c:v>
+                  <c:v>6630400</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5601360</c:v>
+                  <c:v>7491360</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2256,8 +2265,8 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="47119816"/>
-        <c:axId val="80589935"/>
+        <c:axId val="64088234"/>
+        <c:axId val="30271619"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2346,19 +2355,19 @@
                   <c:v>-54700000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-50941387.5</c:v>
+                  <c:v>-50131387.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-45918803.75</c:v>
+                  <c:v>-43920803.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-39350460</c:v>
+                  <c:v>-35840460</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-34448060</c:v>
+                  <c:v>-29210060</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-28846700</c:v>
+                  <c:v>-21718700</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2373,11 +2382,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="47119816"/>
-        <c:axId val="80589935"/>
+        <c:axId val="64088234"/>
+        <c:axId val="30271619"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="47119816"/>
+        <c:axId val="64088234"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2409,7 +2418,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80589935"/>
+        <c:crossAx val="30271619"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2417,7 +2426,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="80589935"/>
+        <c:axId val="30271619"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2493,7 +2502,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47119816"/>
+        <c:crossAx val="64088234"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2597,13 +2606,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>263160</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>262800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>781200</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>144360</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -2612,7 +2621,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="222120" y="4896000"/>
+        <a:off x="222120" y="5086440"/>
         <a:ext cx="5759640" cy="2519640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -3063,7 +3072,7 @@
         <v>31</v>
       </c>
       <c r="C14" s="8" t="n">
-        <f aca="false">SUM('Sanctuary P&amp;L'!C12:G12)</f>
+        <f aca="false">SUM('Sanctuary P&amp;L'!C13:G13)</f>
         <v>9111500</v>
       </c>
     </row>
@@ -3073,7 +3082,7 @@
       </c>
       <c r="C15" s="8" t="n">
         <f aca="false">'Cash Flow'!D8</f>
-        <v>3758612.5</v>
+        <v>4568612.5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3082,7 +3091,7 @@
       </c>
       <c r="C16" s="8" t="n">
         <f aca="false">'Cash Flow'!H8</f>
-        <v>5601360</v>
+        <v>7491360</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3091,7 +3100,7 @@
       </c>
       <c r="C17" s="8" t="n">
         <f aca="false">'Cash Flow'!H9</f>
-        <v>-28846700</v>
+        <v>-21718700</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3144,23 +3153,23 @@
       </c>
       <c r="D21" s="8" t="n">
         <f aca="false">'Cash Flow'!D8</f>
-        <v>3758612.5</v>
+        <v>4568612.5</v>
       </c>
       <c r="E21" s="8" t="n">
         <f aca="false">'Cash Flow'!E8</f>
-        <v>5022583.75</v>
+        <v>6210583.75</v>
       </c>
       <c r="F21" s="8" t="n">
         <f aca="false">'Cash Flow'!F8</f>
-        <v>6568343.75</v>
+        <v>8080343.75</v>
       </c>
       <c r="G21" s="8" t="n">
         <f aca="false">'Cash Flow'!G8</f>
-        <v>4902400</v>
+        <v>6630400</v>
       </c>
       <c r="H21" s="8" t="n">
         <f aca="false">'Cash Flow'!H8</f>
-        <v>5601360</v>
+        <v>7491360</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3173,23 +3182,23 @@
       </c>
       <c r="D22" s="8" t="n">
         <f aca="false">'Cash Flow'!D9</f>
-        <v>-50941387.5</v>
+        <v>-50131387.5</v>
       </c>
       <c r="E22" s="8" t="n">
         <f aca="false">'Cash Flow'!E9</f>
-        <v>-45918803.75</v>
+        <v>-43920803.75</v>
       </c>
       <c r="F22" s="8" t="n">
         <f aca="false">'Cash Flow'!F9</f>
-        <v>-39350460</v>
+        <v>-35840460</v>
       </c>
       <c r="G22" s="8" t="n">
         <f aca="false">'Cash Flow'!G9</f>
-        <v>-34448060</v>
+        <v>-29210060</v>
       </c>
       <c r="H22" s="8" t="n">
         <f aca="false">'Cash Flow'!H9</f>
-        <v>-28846700</v>
+        <v>-21718700</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4931,7 +4940,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:H25"/>
+  <dimension ref="B1:H26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.5"/>
@@ -5114,255 +5123,286 @@
         <v>182</v>
       </c>
       <c r="C12" s="8" t="n">
+        <f aca="false">Assumptions!$C$19*Assumptions!$C$28*12</f>
+        <v>810000</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <f aca="false">Assumptions!$D$19*Assumptions!$C$28*12</f>
+        <v>1188000</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <f aca="false">Assumptions!$E$19*Assumptions!$C$28*12</f>
+        <v>1512000</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <f aca="false">Assumptions!$F$19*Assumptions!$C$28*12</f>
+        <v>1728000</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <f aca="false">Assumptions!$G$19*Assumptions!$C$28*12</f>
+        <v>1890000</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" s="8" t="n">
         <f aca="false">MAX(IFERROR('32-rai Economics'!$C$25*((Assumptions!$C$55)-(0))/Assumptions!$G$55,0),0)</f>
         <v>3416812.5</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D13" s="8" t="n">
         <f aca="false">MAX(IFERROR('32-rai Economics'!$C$25*((Assumptions!$D$55)-(Assumptions!$C$55))/Assumptions!$G$55,0),0)</f>
         <v>2847343.75</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E13" s="8" t="n">
         <f aca="false">MAX(IFERROR('32-rai Economics'!$C$25*((Assumptions!$E$55)-(Assumptions!$D$55))/Assumptions!$G$55,0),0)</f>
         <v>2847343.75</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F13" s="8" t="n">
         <f aca="false">MAX(IFERROR('32-rai Economics'!$C$25*((Assumptions!$F$55)-(Assumptions!$E$55))/Assumptions!$G$55,0),0)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G13" s="8" t="n">
         <f aca="false">MAX(IFERROR('32-rai Economics'!$C$25*((Assumptions!$G$55)-(Assumptions!$F$55))/Assumptions!$G$55,0),0)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="11" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="C13" s="28" t="n">
-        <f aca="false">SUM(C7:C12)</f>
-        <v>8996812.5</v>
-      </c>
-      <c r="D13" s="28" t="n">
-        <f aca="false">SUM(D7:D12)</f>
-        <v>10947343.75</v>
-      </c>
-      <c r="E13" s="28" t="n">
-        <f aca="false">SUM(E7:E12)</f>
-        <v>13167343.75</v>
-      </c>
-      <c r="F13" s="28" t="n">
-        <f aca="false">SUM(F7:F12)</f>
-        <v>12080000</v>
-      </c>
-      <c r="G13" s="28" t="n">
-        <f aca="false">SUM(G7:G12)</f>
-        <v>13440000</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5" t="s">
+      <c r="H13" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="40" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C14" s="28" t="n">
+        <f aca="false">SUM(C7:C13)</f>
+        <v>9806812.5</v>
+      </c>
+      <c r="D14" s="28" t="n">
+        <f aca="false">SUM(D7:D13)</f>
+        <v>12135343.75</v>
+      </c>
+      <c r="E14" s="28" t="n">
+        <f aca="false">SUM(E7:E13)</f>
+        <v>14679343.75</v>
+      </c>
+      <c r="F14" s="28" t="n">
+        <f aca="false">SUM(F7:F13)</f>
+        <v>13808000</v>
+      </c>
+      <c r="G14" s="28" t="n">
+        <f aca="false">SUM(G7:G13)</f>
+        <v>15330000</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="C17" s="8" t="n">
         <f aca="false">Assumptions!$C$34</f>
         <v>3200000</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D17" s="8" t="n">
         <f aca="false">Assumptions!$D$34</f>
         <v>3600000</v>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="E17" s="8" t="n">
         <f aca="false">Assumptions!$E$34</f>
         <v>4000000</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F17" s="8" t="n">
         <f aca="false">Assumptions!$F$34</f>
         <v>4300000</v>
       </c>
-      <c r="G16" s="8" t="n">
+      <c r="G17" s="8" t="n">
         <f aca="false">Assumptions!$G$34</f>
         <v>4600000</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="40" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C18" s="8" t="n">
         <f aca="false">Assumptions!$C$35</f>
         <v>600000</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D18" s="8" t="n">
         <f aca="false">Assumptions!$D$35</f>
         <v>900000</v>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E18" s="8" t="n">
         <f aca="false">Assumptions!$E$35</f>
         <v>1200000</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F18" s="8" t="n">
         <f aca="false">Assumptions!$F$35</f>
         <v>1400000</v>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="G18" s="8" t="n">
         <f aca="false">Assumptions!$G$35</f>
         <v>1600000</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="40" t="s">
-        <v>187</v>
-      </c>
-      <c r="C18" s="8" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19" s="8" t="n">
         <f aca="false">Assumptions!$C$19*Assumptions!$C$28*12</f>
         <v>810000</v>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D19" s="8" t="n">
         <f aca="false">Assumptions!$D$19*Assumptions!$C$28*12</f>
         <v>1188000</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="E19" s="8" t="n">
         <f aca="false">Assumptions!$E$19*Assumptions!$C$28*12</f>
         <v>1512000</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F19" s="8" t="n">
         <f aca="false">Assumptions!$F$19*Assumptions!$C$28*12</f>
         <v>1728000</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G19" s="8" t="n">
         <f aca="false">Assumptions!$G$19*Assumptions!$C$28*12</f>
         <v>1890000</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="40" t="s">
+      <c r="H19" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C20" s="8" t="n">
         <f aca="false">Assumptions!$C$36</f>
         <v>350000</v>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D20" s="8" t="n">
         <f aca="false">Assumptions!$D$36</f>
         <v>400000</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E20" s="8" t="n">
         <f aca="false">Assumptions!$E$36</f>
         <v>450000</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F20" s="8" t="n">
         <f aca="false">Assumptions!$F$36</f>
         <v>480000</v>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="G20" s="8" t="n">
         <f aca="false">Assumptions!$G$36</f>
         <v>500000</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="40" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C21" s="8" t="n">
         <f aca="false">Assumptions!$C$37</f>
         <v>300000</v>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D21" s="8" t="n">
         <f aca="false">Assumptions!$D$37</f>
         <v>320000</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E21" s="8" t="n">
         <f aca="false">Assumptions!$E$37</f>
         <v>340000</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F21" s="8" t="n">
         <f aca="false">Assumptions!$F$37</f>
         <v>360000</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G21" s="8" t="n">
         <f aca="false">Assumptions!$G$37</f>
         <v>380000</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="C21" s="28" t="n">
-        <f aca="false">SUM(C16:C20)</f>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="C22" s="28" t="n">
+        <f aca="false">SUM(C17:C21)</f>
         <v>5260000</v>
       </c>
-      <c r="D21" s="28" t="n">
-        <f aca="false">SUM(D16:D20)</f>
+      <c r="D22" s="28" t="n">
+        <f aca="false">SUM(D17:D21)</f>
         <v>6408000</v>
       </c>
-      <c r="E21" s="28" t="n">
-        <f aca="false">SUM(E16:E20)</f>
+      <c r="E22" s="28" t="n">
+        <f aca="false">SUM(E17:E21)</f>
         <v>7502000</v>
       </c>
-      <c r="F21" s="28" t="n">
-        <f aca="false">SUM(F16:F20)</f>
+      <c r="F22" s="28" t="n">
+        <f aca="false">SUM(F17:F21)</f>
         <v>8268000</v>
       </c>
-      <c r="G21" s="28" t="n">
-        <f aca="false">SUM(G16:G20)</f>
+      <c r="G22" s="28" t="n">
+        <f aca="false">SUM(G17:G21)</f>
         <v>8970000</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="C23" s="28" t="n">
-        <f aca="false">C13-C21</f>
-        <v>3736812.5</v>
-      </c>
-      <c r="D23" s="28" t="n">
-        <f aca="false">D13-D21</f>
-        <v>4539343.75</v>
-      </c>
-      <c r="E23" s="28" t="n">
-        <f aca="false">E13-E21</f>
-        <v>5665343.75</v>
-      </c>
-      <c r="F23" s="28" t="n">
-        <f aca="false">F13-F21</f>
-        <v>3812000</v>
-      </c>
-      <c r="G23" s="28" t="n">
-        <f aca="false">G13-G21</f>
-        <v>4470000</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="C24" s="28" t="n">
+        <f aca="false">C14-C22</f>
+        <v>4546812.5</v>
+      </c>
+      <c r="D24" s="28" t="n">
+        <f aca="false">D14-D22</f>
+        <v>5727343.75</v>
+      </c>
+      <c r="E24" s="28" t="n">
+        <f aca="false">E14-E22</f>
+        <v>7177343.75</v>
+      </c>
+      <c r="F24" s="28" t="n">
+        <f aca="false">F14-F22</f>
+        <v>5540000</v>
+      </c>
+      <c r="G24" s="28" t="n">
+        <f aca="false">G14-G22</f>
+        <v>6360000</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B26:G26"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5391,12 +5431,12 @@
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5435,7 +5475,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="40" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">Assumptions!$C$40*Assumptions!$C$43*Assumptions!$C$41*365</f>
@@ -5460,7 +5500,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="40" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">Assumptions!$C$44*Assumptions!$C$47*Assumptions!$C$45*365</f>
@@ -5485,7 +5525,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="40" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C9" s="8" t="n">
         <f aca="false">Assumptions!$C$48*Assumptions!$C$51*Assumptions!$C$49*365</f>
@@ -5510,7 +5550,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="40" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C10" s="8" t="n">
         <f aca="false">Assumptions!$C$20*Assumptions!$C$56+Assumptions!$C$55*Assumptions!$C$57</f>
@@ -5535,7 +5575,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="40" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C11" s="8" t="n">
         <f aca="false">Assumptions!$C$55*Assumptions!$C$58</f>
@@ -5560,7 +5600,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="35" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C12" s="36" t="n">
         <f aca="false">SUM(C7:C11)</f>
@@ -5585,7 +5625,7 @@
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="20" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
@@ -5596,7 +5636,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="40" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C15" s="8" t="n">
         <f aca="false">Assumptions!$C$59</f>
@@ -5621,7 +5661,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="40" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C16" s="8" t="n">
         <f aca="false">Assumptions!$C$60</f>
@@ -5646,7 +5686,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="35" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C17" s="36" t="n">
         <f aca="false">SUM(C15:C16)</f>
@@ -5671,7 +5711,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="35" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C19" s="36" t="n">
         <f aca="false">C12-C17</f>
@@ -5725,12 +5765,12 @@
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5738,7 +5778,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>56</v>
@@ -5758,7 +5798,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">-'Sanctuary Capex'!C19</f>
@@ -5782,30 +5822,30 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="8" t="n">
-        <f aca="false">'Sanctuary P&amp;L'!C23+'Community P&amp;L'!C19</f>
-        <v>3758612.5</v>
+        <f aca="false">'Sanctuary P&amp;L'!C24+'Community P&amp;L'!C19</f>
+        <v>4568612.5</v>
       </c>
       <c r="E7" s="8" t="n">
-        <f aca="false">'Sanctuary P&amp;L'!D23+'Community P&amp;L'!D19</f>
-        <v>5022583.75</v>
+        <f aca="false">'Sanctuary P&amp;L'!D24+'Community P&amp;L'!D19</f>
+        <v>6210583.75</v>
       </c>
       <c r="F7" s="8" t="n">
-        <f aca="false">'Sanctuary P&amp;L'!E23+'Community P&amp;L'!E19</f>
-        <v>6568343.75</v>
+        <f aca="false">'Sanctuary P&amp;L'!E24+'Community P&amp;L'!E19</f>
+        <v>8080343.75</v>
       </c>
       <c r="G7" s="8" t="n">
-        <f aca="false">'Sanctuary P&amp;L'!F23+'Community P&amp;L'!F19</f>
-        <v>4902400</v>
+        <f aca="false">'Sanctuary P&amp;L'!F24+'Community P&amp;L'!F19</f>
+        <v>6630400</v>
       </c>
       <c r="H7" s="8" t="n">
-        <f aca="false">'Sanctuary P&amp;L'!G23+'Community P&amp;L'!G19</f>
-        <v>5601360</v>
+        <f aca="false">'Sanctuary P&amp;L'!G24+'Community P&amp;L'!G19</f>
+        <v>7491360</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5818,23 +5858,23 @@
       </c>
       <c r="D8" s="28" t="n">
         <f aca="false">D6+D7</f>
-        <v>3758612.5</v>
+        <v>4568612.5</v>
       </c>
       <c r="E8" s="28" t="n">
         <f aca="false">E6+E7</f>
-        <v>5022583.75</v>
+        <v>6210583.75</v>
       </c>
       <c r="F8" s="28" t="n">
         <f aca="false">F6+F7</f>
-        <v>6568343.75</v>
+        <v>8080343.75</v>
       </c>
       <c r="G8" s="28" t="n">
         <f aca="false">G6+G7</f>
-        <v>4902400</v>
+        <v>6630400</v>
       </c>
       <c r="H8" s="28" t="n">
         <f aca="false">H6+H7</f>
-        <v>5601360</v>
+        <v>7491360</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5847,33 +5887,33 @@
       </c>
       <c r="D9" s="36" t="n">
         <f aca="false">C9+D8</f>
-        <v>-50941387.5</v>
+        <v>-50131387.5</v>
       </c>
       <c r="E9" s="36" t="n">
         <f aca="false">D9+E8</f>
-        <v>-45918803.75</v>
+        <v>-43920803.75</v>
       </c>
       <c r="F9" s="36" t="n">
         <f aca="false">E9+F8</f>
-        <v>-39350460</v>
+        <v>-35840460</v>
       </c>
       <c r="G9" s="36" t="n">
         <f aca="false">F9+G8</f>
-        <v>-34448060</v>
+        <v>-29210060</v>
       </c>
       <c r="H9" s="36" t="n">
         <f aca="false">G9+H8</f>
-        <v>-28846700</v>
+        <v>-21718700</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="34" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="34" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/business-plan/model/Angel_Arms_Financial_Model.xlsx
+++ b/business-plan/model/Angel_Arms_Financial_Model.xlsx
@@ -216,7 +216,7 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">Horses in residence</t>
+    <t xml:space="preserve">Horses in residence (capped at 20)</t>
   </si>
   <si>
     <t xml:space="preserve">Visitors (tours, per year)</t>
@@ -246,6 +246,9 @@
     <t xml:space="preserve">Vet fees are billed directly to the owner — not in this model</t>
   </si>
   <si>
+    <t xml:space="preserve">Sanctuary manager salary (THB / month, all other staff volunteer)</t>
+  </si>
+  <si>
     <t xml:space="preserve">SANCTUARY — DONATIONS, GRANTS, STAFF &amp; OPEX (per year)</t>
   </si>
   <si>
@@ -255,10 +258,7 @@
     <t xml:space="preserve">Therapy program CSR / grants</t>
   </si>
   <si>
-    <t xml:space="preserve">Sanctuary staff cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Therapy program staff / equipment</t>
+    <t xml:space="preserve">Therapy program staff / equipment (volunteer staff; kept at ฿0 — flag if equipment budget still needed)</t>
   </si>
   <si>
     <t xml:space="preserve">Utilities / maintenance</t>
@@ -312,7 +312,7 @@
     <t xml:space="preserve">HOA fee per plot / year (THB)</t>
   </si>
   <si>
-    <t xml:space="preserve">Community staff cost</t>
+    <t xml:space="preserve">Community staff / hospitality (volunteer)</t>
   </si>
   <si>
     <t xml:space="preserve">Community upkeep cost</t>
@@ -594,7 +594,10 @@
     <t xml:space="preserve">OPERATING COST</t>
   </si>
   <si>
-    <t xml:space="preserve">Sanctuary staff</t>
+    <t xml:space="preserve">Sanctuary manager (fixed; all other staff volunteer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Therapy program staff / equipment (volunteer)</t>
   </si>
   <si>
     <t xml:space="preserve">Feed / routine care (horses × ฿ /mo × 12)</t>
@@ -631,9 +634,6 @@
   </si>
   <si>
     <t xml:space="preserve">HOA / common-area fee (plots sold × fee)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Community staff / hospitality</t>
   </si>
   <si>
     <t xml:space="preserve">Community upkeep</t>
@@ -1282,19 +1282,19 @@
                   <c:v>-54700000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4568612.5</c:v>
+                  <c:v>8968612.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6210583.75</c:v>
+                  <c:v>11150583.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8080343.75</c:v>
+                  <c:v>12840343.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6630400</c:v>
+                  <c:v>11270400</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7491360</c:v>
+                  <c:v>12141360</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1302,8 +1302,8 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="60346967"/>
-        <c:axId val="7962686"/>
+        <c:axId val="92768975"/>
+        <c:axId val="8601213"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -1392,19 +1392,19 @@
                   <c:v>-54700000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-50131387.5</c:v>
+                  <c:v>-45731387.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-43920803.75</c:v>
+                  <c:v>-34580803.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-35840460</c:v>
+                  <c:v>-21740460</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-29210060</c:v>
+                  <c:v>-10470060</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-21718700</c:v>
+                  <c:v>1671300</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1419,11 +1419,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="60346967"/>
-        <c:axId val="7962686"/>
+        <c:axId val="92768975"/>
+        <c:axId val="8601213"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="60346967"/>
+        <c:axId val="92768975"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1455,7 +1455,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7962686"/>
+        <c:crossAx val="8601213"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1463,7 +1463,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="7962686"/>
+        <c:axId val="8601213"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1539,7 +1539,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60346967"/>
+        <c:crossAx val="92768975"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1750,11 +1750,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="83682299"/>
-        <c:axId val="62088960"/>
+        <c:axId val="26294243"/>
+        <c:axId val="60661255"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="83682299"/>
+        <c:axId val="26294243"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1786,7 +1786,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62088960"/>
+        <c:crossAx val="60661255"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1794,7 +1794,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="62088960"/>
+        <c:axId val="60661255"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1836,7 +1836,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83682299"/>
+        <c:crossAx val="26294243"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1986,19 +1986,19 @@
                 <c:formatCode>\฿#,##0;"(฿"#,##0\);\-</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>4546812.5</c:v>
+                  <c:v>8046812.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5727343.75</c:v>
+                  <c:v>9567343.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7177343.75</c:v>
+                  <c:v>10637343.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5540000</c:v>
+                  <c:v>8780000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6360000</c:v>
+                  <c:v>9560000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2013,11 +2013,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="28798824"/>
-        <c:axId val="47955744"/>
+        <c:axId val="94265574"/>
+        <c:axId val="68874252"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="28798824"/>
+        <c:axId val="94265574"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2049,7 +2049,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47955744"/>
+        <c:crossAx val="68874252"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2057,7 +2057,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="47955744"/>
+        <c:axId val="68874252"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2099,7 +2099,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28798824"/>
+        <c:crossAx val="94265574"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2245,19 +2245,19 @@
                   <c:v>-54700000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4568612.5</c:v>
+                  <c:v>8968612.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6210583.75</c:v>
+                  <c:v>11150583.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8080343.75</c:v>
+                  <c:v>12840343.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6630400</c:v>
+                  <c:v>11270400</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7491360</c:v>
+                  <c:v>12141360</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2265,8 +2265,8 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="64088234"/>
-        <c:axId val="30271619"/>
+        <c:axId val="67871455"/>
+        <c:axId val="79042439"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2355,19 +2355,19 @@
                   <c:v>-54700000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-50131387.5</c:v>
+                  <c:v>-45731387.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-43920803.75</c:v>
+                  <c:v>-34580803.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-35840460</c:v>
+                  <c:v>-21740460</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-29210060</c:v>
+                  <c:v>-10470060</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-21718700</c:v>
+                  <c:v>1671300</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2382,11 +2382,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="64088234"/>
-        <c:axId val="30271619"/>
+        <c:axId val="67871455"/>
+        <c:axId val="79042439"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="64088234"/>
+        <c:axId val="67871455"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2418,7 +2418,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30271619"/>
+        <c:crossAx val="79042439"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2426,7 +2426,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30271619"/>
+        <c:axId val="79042439"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2502,7 +2502,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64088234"/>
+        <c:crossAx val="67871455"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="C15" s="8" t="n">
         <f aca="false">'Cash Flow'!D8</f>
-        <v>4568612.5</v>
+        <v>8968612.5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="C16" s="8" t="n">
         <f aca="false">'Cash Flow'!H8</f>
-        <v>7491360</v>
+        <v>12141360</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="C17" s="8" t="n">
         <f aca="false">'Cash Flow'!H9</f>
-        <v>-21718700</v>
+        <v>1671300</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3153,23 +3153,23 @@
       </c>
       <c r="D21" s="8" t="n">
         <f aca="false">'Cash Flow'!D8</f>
-        <v>4568612.5</v>
+        <v>8968612.5</v>
       </c>
       <c r="E21" s="8" t="n">
         <f aca="false">'Cash Flow'!E8</f>
-        <v>6210583.75</v>
+        <v>11150583.75</v>
       </c>
       <c r="F21" s="8" t="n">
         <f aca="false">'Cash Flow'!F8</f>
-        <v>8080343.75</v>
+        <v>12840343.75</v>
       </c>
       <c r="G21" s="8" t="n">
         <f aca="false">'Cash Flow'!G8</f>
-        <v>6630400</v>
+        <v>11270400</v>
       </c>
       <c r="H21" s="8" t="n">
         <f aca="false">'Cash Flow'!H8</f>
-        <v>7491360</v>
+        <v>12141360</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3182,23 +3182,23 @@
       </c>
       <c r="D22" s="8" t="n">
         <f aca="false">'Cash Flow'!D9</f>
-        <v>-50131387.5</v>
+        <v>-45731387.5</v>
       </c>
       <c r="E22" s="8" t="n">
         <f aca="false">'Cash Flow'!E9</f>
-        <v>-43920803.75</v>
+        <v>-34580803.75</v>
       </c>
       <c r="F22" s="8" t="n">
         <f aca="false">'Cash Flow'!F9</f>
-        <v>-35840460</v>
+        <v>-21740460</v>
       </c>
       <c r="G22" s="8" t="n">
         <f aca="false">'Cash Flow'!G9</f>
-        <v>-29210060</v>
+        <v>-10470060</v>
       </c>
       <c r="H22" s="8" t="n">
         <f aca="false">'Cash Flow'!H9</f>
-        <v>-21718700</v>
+        <v>1671300</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3386,16 +3386,16 @@
         <v>15</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3492,58 +3492,46 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="5" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-    </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="9" t="s">
+      <c r="C29" s="12" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+    </row>
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C32" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D32" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E32" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="F31" s="17" t="s">
+      <c r="F32" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="G31" s="17" t="s">
+      <c r="G32" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="H32" s="9" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" s="18" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="G32" s="18" t="n">
-        <v>2000000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3551,19 +3539,19 @@
         <v>74</v>
       </c>
       <c r="C33" s="18" t="n">
-        <v>800000</v>
+        <v>1200000</v>
       </c>
       <c r="D33" s="18" t="n">
-        <v>1200000</v>
+        <v>1400000</v>
       </c>
       <c r="E33" s="18" t="n">
-        <v>1700000</v>
+        <v>1600000</v>
       </c>
       <c r="F33" s="18" t="n">
-        <v>2100000</v>
+        <v>1800000</v>
       </c>
       <c r="G33" s="18" t="n">
-        <v>2500000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3571,39 +3559,39 @@
         <v>75</v>
       </c>
       <c r="C34" s="18" t="n">
-        <v>3200000</v>
+        <v>800000</v>
       </c>
       <c r="D34" s="18" t="n">
-        <v>3600000</v>
+        <v>1200000</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>4000000</v>
+        <v>1700000</v>
       </c>
       <c r="F34" s="18" t="n">
-        <v>4300000</v>
+        <v>2100000</v>
       </c>
       <c r="G34" s="18" t="n">
-        <v>4600000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="18" t="n">
-        <v>600000</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>900000</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="F35" s="18" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="G35" s="18" t="n">
-        <v>1600000</v>
+      <c r="C35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3916,20 +3904,20 @@
       <c r="B59" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C59" s="18" t="n">
-        <v>900000</v>
-      </c>
-      <c r="D59" s="18" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="E59" s="18" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="F59" s="18" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="G59" s="18" t="n">
-        <v>1450000</v>
+      <c r="C59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4199,7 +4187,7 @@
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="B23:H23"/>
-    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="B31:H31"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B53:H53"/>
     <mergeCell ref="B62:H62"/>
@@ -5003,19 +4991,19 @@
       </c>
       <c r="D7" s="8" t="n">
         <f aca="false">Assumptions!$D$19*Assumptions!$C$24*12</f>
-        <v>3960000</v>
+        <v>3600000</v>
       </c>
       <c r="E7" s="8" t="n">
         <f aca="false">Assumptions!$E$19*Assumptions!$C$24*12</f>
-        <v>5040000</v>
+        <v>3600000</v>
       </c>
       <c r="F7" s="8" t="n">
         <f aca="false">Assumptions!$F$19*Assumptions!$C$24*12</f>
-        <v>5760000</v>
+        <v>3600000</v>
       </c>
       <c r="G7" s="8" t="n">
         <f aca="false">Assumptions!$G$19*Assumptions!$C$24*12</f>
-        <v>6300000</v>
+        <v>3600000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5070,51 +5058,51 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10" s="8" t="n">
-        <f aca="false">Assumptions!$C$32</f>
+        <f aca="false">Assumptions!$C$33</f>
         <v>1200000</v>
       </c>
       <c r="D10" s="8" t="n">
-        <f aca="false">Assumptions!$D$32</f>
+        <f aca="false">Assumptions!$D$33</f>
         <v>1400000</v>
       </c>
       <c r="E10" s="8" t="n">
-        <f aca="false">Assumptions!$E$32</f>
+        <f aca="false">Assumptions!$E$33</f>
         <v>1600000</v>
       </c>
       <c r="F10" s="8" t="n">
-        <f aca="false">Assumptions!$F$32</f>
+        <f aca="false">Assumptions!$F$33</f>
         <v>1800000</v>
       </c>
       <c r="G10" s="8" t="n">
-        <f aca="false">Assumptions!$G$32</f>
+        <f aca="false">Assumptions!$G$33</f>
         <v>2000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="40" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C11" s="8" t="n">
-        <f aca="false">Assumptions!$C$33</f>
+        <f aca="false">Assumptions!$C$34</f>
         <v>800000</v>
       </c>
       <c r="D11" s="8" t="n">
-        <f aca="false">Assumptions!$D$33</f>
+        <f aca="false">Assumptions!$D$34</f>
         <v>1200000</v>
       </c>
       <c r="E11" s="8" t="n">
-        <f aca="false">Assumptions!$E$33</f>
+        <f aca="false">Assumptions!$E$34</f>
         <v>1700000</v>
       </c>
       <c r="F11" s="8" t="n">
-        <f aca="false">Assumptions!$F$33</f>
+        <f aca="false">Assumptions!$F$34</f>
         <v>2100000</v>
       </c>
       <c r="G11" s="8" t="n">
-        <f aca="false">Assumptions!$G$33</f>
+        <f aca="false">Assumptions!$G$34</f>
         <v>2500000</v>
       </c>
     </row>
@@ -5128,19 +5116,19 @@
       </c>
       <c r="D12" s="8" t="n">
         <f aca="false">Assumptions!$D$19*Assumptions!$C$28*12</f>
-        <v>1188000</v>
+        <v>1080000</v>
       </c>
       <c r="E12" s="8" t="n">
         <f aca="false">Assumptions!$E$19*Assumptions!$C$28*12</f>
-        <v>1512000</v>
+        <v>1080000</v>
       </c>
       <c r="F12" s="8" t="n">
         <f aca="false">Assumptions!$F$19*Assumptions!$C$28*12</f>
-        <v>1728000</v>
+        <v>1080000</v>
       </c>
       <c r="G12" s="8" t="n">
         <f aca="false">Assumptions!$G$19*Assumptions!$C$28*12</f>
-        <v>1890000</v>
+        <v>1080000</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>183</v>
@@ -5184,19 +5172,19 @@
       </c>
       <c r="D14" s="28" t="n">
         <f aca="false">SUM(D7:D13)</f>
-        <v>12135343.75</v>
+        <v>11667343.75</v>
       </c>
       <c r="E14" s="28" t="n">
         <f aca="false">SUM(E7:E13)</f>
-        <v>14679343.75</v>
+        <v>12807343.75</v>
       </c>
       <c r="F14" s="28" t="n">
         <f aca="false">SUM(F7:F13)</f>
-        <v>13808000</v>
+        <v>11000000</v>
       </c>
       <c r="G14" s="28" t="n">
         <f aca="false">SUM(G7:G13)</f>
-        <v>15330000</v>
+        <v>11820000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5215,54 +5203,54 @@
         <v>188</v>
       </c>
       <c r="C17" s="8" t="n">
-        <f aca="false">Assumptions!$C$34</f>
-        <v>3200000</v>
+        <f aca="false">Assumptions!$C$29*12</f>
+        <v>300000</v>
       </c>
       <c r="D17" s="8" t="n">
-        <f aca="false">Assumptions!$D$34</f>
-        <v>3600000</v>
+        <f aca="false">Assumptions!$C$29*12</f>
+        <v>300000</v>
       </c>
       <c r="E17" s="8" t="n">
-        <f aca="false">Assumptions!$E$34</f>
-        <v>4000000</v>
+        <f aca="false">Assumptions!$C$29*12</f>
+        <v>300000</v>
       </c>
       <c r="F17" s="8" t="n">
-        <f aca="false">Assumptions!$F$34</f>
-        <v>4300000</v>
+        <f aca="false">Assumptions!$C$29*12</f>
+        <v>300000</v>
       </c>
       <c r="G17" s="8" t="n">
-        <f aca="false">Assumptions!$G$34</f>
-        <v>4600000</v>
+        <f aca="false">Assumptions!$C$29*12</f>
+        <v>300000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="40" t="s">
-        <v>76</v>
+        <v>189</v>
       </c>
       <c r="C18" s="8" t="n">
         <f aca="false">Assumptions!$C$35</f>
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="D18" s="8" t="n">
         <f aca="false">Assumptions!$D$35</f>
-        <v>900000</v>
+        <v>0</v>
       </c>
       <c r="E18" s="8" t="n">
         <f aca="false">Assumptions!$E$35</f>
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="F18" s="8" t="n">
         <f aca="false">Assumptions!$F$35</f>
-        <v>1400000</v>
+        <v>0</v>
       </c>
       <c r="G18" s="8" t="n">
         <f aca="false">Assumptions!$G$35</f>
-        <v>1600000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="40" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C19" s="8" t="n">
         <f aca="false">Assumptions!$C$19*Assumptions!$C$28*12</f>
@@ -5270,22 +5258,22 @@
       </c>
       <c r="D19" s="8" t="n">
         <f aca="false">Assumptions!$D$19*Assumptions!$C$28*12</f>
-        <v>1188000</v>
+        <v>1080000</v>
       </c>
       <c r="E19" s="8" t="n">
         <f aca="false">Assumptions!$E$19*Assumptions!$C$28*12</f>
-        <v>1512000</v>
+        <v>1080000</v>
       </c>
       <c r="F19" s="8" t="n">
         <f aca="false">Assumptions!$F$19*Assumptions!$C$28*12</f>
-        <v>1728000</v>
+        <v>1080000</v>
       </c>
       <c r="G19" s="8" t="n">
         <f aca="false">Assumptions!$G$19*Assumptions!$C$28*12</f>
-        <v>1890000</v>
+        <v>1080000</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5340,57 +5328,57 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="27" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C22" s="28" t="n">
         <f aca="false">SUM(C17:C21)</f>
-        <v>5260000</v>
+        <v>1760000</v>
       </c>
       <c r="D22" s="28" t="n">
         <f aca="false">SUM(D17:D21)</f>
-        <v>6408000</v>
+        <v>2100000</v>
       </c>
       <c r="E22" s="28" t="n">
         <f aca="false">SUM(E17:E21)</f>
-        <v>7502000</v>
+        <v>2170000</v>
       </c>
       <c r="F22" s="28" t="n">
         <f aca="false">SUM(F17:F21)</f>
-        <v>8268000</v>
+        <v>2220000</v>
       </c>
       <c r="G22" s="28" t="n">
         <f aca="false">SUM(G17:G21)</f>
-        <v>8970000</v>
+        <v>2260000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="27" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C24" s="28" t="n">
         <f aca="false">C14-C22</f>
-        <v>4546812.5</v>
+        <v>8046812.5</v>
       </c>
       <c r="D24" s="28" t="n">
         <f aca="false">D14-D22</f>
-        <v>5727343.75</v>
+        <v>9567343.75</v>
       </c>
       <c r="E24" s="28" t="n">
         <f aca="false">E14-E22</f>
-        <v>7177343.75</v>
+        <v>10637343.75</v>
       </c>
       <c r="F24" s="28" t="n">
         <f aca="false">F14-F22</f>
-        <v>5540000</v>
+        <v>8780000</v>
       </c>
       <c r="G24" s="28" t="n">
         <f aca="false">G14-G22</f>
-        <v>6360000</v>
+        <v>9560000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C26" s="29"/>
       <c r="D26" s="29"/>
@@ -5431,12 +5419,12 @@
     <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5475,7 +5463,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="40" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">Assumptions!$C$40*Assumptions!$C$43*Assumptions!$C$41*365</f>
@@ -5500,7 +5488,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="40" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">Assumptions!$C$44*Assumptions!$C$47*Assumptions!$C$45*365</f>
@@ -5525,7 +5513,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="40" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C9" s="8" t="n">
         <f aca="false">Assumptions!$C$48*Assumptions!$C$51*Assumptions!$C$49*365</f>
@@ -5550,7 +5538,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="40" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C10" s="8" t="n">
         <f aca="false">Assumptions!$C$20*Assumptions!$C$56+Assumptions!$C$55*Assumptions!$C$57</f>
@@ -5575,7 +5563,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C11" s="8" t="n">
         <f aca="false">Assumptions!$C$55*Assumptions!$C$58</f>
@@ -5636,27 +5624,27 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="40" t="s">
-        <v>201</v>
+        <v>94</v>
       </c>
       <c r="C15" s="8" t="n">
         <f aca="false">Assumptions!$C$59</f>
-        <v>900000</v>
+        <v>0</v>
       </c>
       <c r="D15" s="8" t="n">
         <f aca="false">Assumptions!$D$59</f>
-        <v>1100000</v>
+        <v>0</v>
       </c>
       <c r="E15" s="8" t="n">
         <f aca="false">Assumptions!$E$59</f>
-        <v>1300000</v>
+        <v>0</v>
       </c>
       <c r="F15" s="8" t="n">
         <f aca="false">Assumptions!$F$59</f>
-        <v>1400000</v>
+        <v>0</v>
       </c>
       <c r="G15" s="8" t="n">
         <f aca="false">Assumptions!$G$59</f>
-        <v>1450000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5686,27 +5674,27 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="35" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C17" s="36" t="n">
         <f aca="false">SUM(C15:C16)</f>
-        <v>1100000</v>
+        <v>200000</v>
       </c>
       <c r="D17" s="36" t="n">
         <f aca="false">SUM(D15:D16)</f>
-        <v>1450000</v>
+        <v>350000</v>
       </c>
       <c r="E17" s="36" t="n">
         <f aca="false">SUM(E15:E16)</f>
-        <v>1800000</v>
+        <v>500000</v>
       </c>
       <c r="F17" s="36" t="n">
         <f aca="false">SUM(F15:F16)</f>
-        <v>1950000</v>
+        <v>550000</v>
       </c>
       <c r="G17" s="36" t="n">
         <f aca="false">SUM(G15:G16)</f>
-        <v>2050000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5715,23 +5703,23 @@
       </c>
       <c r="C19" s="36" t="n">
         <f aca="false">C12-C17</f>
-        <v>21800</v>
+        <v>921800</v>
       </c>
       <c r="D19" s="36" t="n">
         <f aca="false">D12-D17</f>
-        <v>483240</v>
+        <v>1583240</v>
       </c>
       <c r="E19" s="36" t="n">
         <f aca="false">E12-E17</f>
-        <v>903000</v>
+        <v>2203000</v>
       </c>
       <c r="F19" s="36" t="n">
         <f aca="false">F12-F17</f>
-        <v>1090400</v>
+        <v>2490400</v>
       </c>
       <c r="G19" s="36" t="n">
         <f aca="false">G12-G17</f>
-        <v>1131360</v>
+        <v>2581360</v>
       </c>
     </row>
   </sheetData>
@@ -5829,23 +5817,23 @@
       </c>
       <c r="D7" s="8" t="n">
         <f aca="false">'Sanctuary P&amp;L'!C24+'Community P&amp;L'!C19</f>
-        <v>4568612.5</v>
+        <v>8968612.5</v>
       </c>
       <c r="E7" s="8" t="n">
         <f aca="false">'Sanctuary P&amp;L'!D24+'Community P&amp;L'!D19</f>
-        <v>6210583.75</v>
+        <v>11150583.75</v>
       </c>
       <c r="F7" s="8" t="n">
         <f aca="false">'Sanctuary P&amp;L'!E24+'Community P&amp;L'!E19</f>
-        <v>8080343.75</v>
+        <v>12840343.75</v>
       </c>
       <c r="G7" s="8" t="n">
         <f aca="false">'Sanctuary P&amp;L'!F24+'Community P&amp;L'!F19</f>
-        <v>6630400</v>
+        <v>11270400</v>
       </c>
       <c r="H7" s="8" t="n">
         <f aca="false">'Sanctuary P&amp;L'!G24+'Community P&amp;L'!G19</f>
-        <v>7491360</v>
+        <v>12141360</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5858,23 +5846,23 @@
       </c>
       <c r="D8" s="28" t="n">
         <f aca="false">D6+D7</f>
-        <v>4568612.5</v>
+        <v>8968612.5</v>
       </c>
       <c r="E8" s="28" t="n">
         <f aca="false">E6+E7</f>
-        <v>6210583.75</v>
+        <v>11150583.75</v>
       </c>
       <c r="F8" s="28" t="n">
         <f aca="false">F6+F7</f>
-        <v>8080343.75</v>
+        <v>12840343.75</v>
       </c>
       <c r="G8" s="28" t="n">
         <f aca="false">G6+G7</f>
-        <v>6630400</v>
+        <v>11270400</v>
       </c>
       <c r="H8" s="28" t="n">
         <f aca="false">H6+H7</f>
-        <v>7491360</v>
+        <v>12141360</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5887,23 +5875,23 @@
       </c>
       <c r="D9" s="36" t="n">
         <f aca="false">C9+D8</f>
-        <v>-50131387.5</v>
+        <v>-45731387.5</v>
       </c>
       <c r="E9" s="36" t="n">
         <f aca="false">D9+E8</f>
-        <v>-43920803.75</v>
+        <v>-34580803.75</v>
       </c>
       <c r="F9" s="36" t="n">
         <f aca="false">E9+F8</f>
-        <v>-35840460</v>
+        <v>-21740460</v>
       </c>
       <c r="G9" s="36" t="n">
         <f aca="false">F9+G8</f>
-        <v>-29210060</v>
+        <v>-10470060</v>
       </c>
       <c r="H9" s="36" t="n">
         <f aca="false">G9+H8</f>
-        <v>-21718700</v>
+        <v>1671300</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
